--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -745,25 +745,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3299700</v>
+        <v>3233700</v>
       </c>
       <c r="E8" s="3">
-        <v>3699700</v>
+        <v>3625700</v>
       </c>
       <c r="F8" s="3">
-        <v>3834200</v>
+        <v>3757500</v>
       </c>
       <c r="G8" s="3">
-        <v>4480500</v>
+        <v>4390800</v>
       </c>
       <c r="H8" s="3">
-        <v>4900600</v>
+        <v>4802600</v>
       </c>
       <c r="I8" s="3">
-        <v>3942900</v>
+        <v>3864000</v>
       </c>
       <c r="J8" s="3">
-        <v>2997400</v>
+        <v>2937400</v>
       </c>
       <c r="K8" s="3">
         <v>2617200</v>
@@ -795,25 +795,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2738200</v>
+        <v>2683400</v>
       </c>
       <c r="E9" s="3">
-        <v>2846000</v>
+        <v>2789000</v>
       </c>
       <c r="F9" s="3">
-        <v>2790400</v>
+        <v>2734600</v>
       </c>
       <c r="G9" s="3">
-        <v>3183100</v>
+        <v>3119400</v>
       </c>
       <c r="H9" s="3">
-        <v>2919700</v>
+        <v>2861300</v>
       </c>
       <c r="I9" s="3">
-        <v>2372000</v>
+        <v>2324600</v>
       </c>
       <c r="J9" s="3">
-        <v>2266100</v>
+        <v>2220700</v>
       </c>
       <c r="K9" s="3">
         <v>2121800</v>
@@ -845,25 +845,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>561500</v>
+        <v>550300</v>
       </c>
       <c r="E10" s="3">
-        <v>853700</v>
+        <v>836600</v>
       </c>
       <c r="F10" s="3">
-        <v>1043800</v>
+        <v>1023000</v>
       </c>
       <c r="G10" s="3">
-        <v>1297400</v>
+        <v>1271400</v>
       </c>
       <c r="H10" s="3">
-        <v>1980900</v>
+        <v>1941300</v>
       </c>
       <c r="I10" s="3">
-        <v>1570900</v>
+        <v>1539500</v>
       </c>
       <c r="J10" s="3">
-        <v>731400</v>
+        <v>716700</v>
       </c>
       <c r="K10" s="3">
         <v>495400</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4600</v>
+        <v>-4500</v>
       </c>
       <c r="E14" s="3">
-        <v>19900</v>
+        <v>19500</v>
       </c>
       <c r="F14" s="3">
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="G14" s="3">
-        <v>289900</v>
+        <v>284100</v>
       </c>
       <c r="H14" s="3">
         <v>2100</v>
       </c>
       <c r="I14" s="3">
-        <v>89600</v>
+        <v>87800</v>
       </c>
       <c r="J14" s="3">
-        <v>22400</v>
+        <v>22000</v>
       </c>
       <c r="K14" s="3">
         <v>51000</v>
@@ -1132,25 +1132,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2735900</v>
+        <v>2681200</v>
       </c>
       <c r="E17" s="3">
-        <v>2871600</v>
+        <v>2814200</v>
       </c>
       <c r="F17" s="3">
-        <v>2804400</v>
+        <v>2748300</v>
       </c>
       <c r="G17" s="3">
-        <v>3477600</v>
+        <v>3408000</v>
       </c>
       <c r="H17" s="3">
-        <v>2940200</v>
+        <v>2881400</v>
       </c>
       <c r="I17" s="3">
-        <v>2473400</v>
+        <v>2423900</v>
       </c>
       <c r="J17" s="3">
-        <v>2304700</v>
+        <v>2258600</v>
       </c>
       <c r="K17" s="3">
         <v>2183400</v>
@@ -1182,25 +1182,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>563800</v>
+        <v>552500</v>
       </c>
       <c r="E18" s="3">
-        <v>828000</v>
+        <v>811500</v>
       </c>
       <c r="F18" s="3">
-        <v>1029900</v>
+        <v>1009300</v>
       </c>
       <c r="G18" s="3">
-        <v>1002900</v>
+        <v>982800</v>
       </c>
       <c r="H18" s="3">
-        <v>1960500</v>
+        <v>1921200</v>
       </c>
       <c r="I18" s="3">
-        <v>1469500</v>
+        <v>1440100</v>
       </c>
       <c r="J18" s="3">
-        <v>692700</v>
+        <v>678900</v>
       </c>
       <c r="K18" s="3">
         <v>433800</v>
@@ -1252,25 +1252,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>54000</v>
+        <v>53000</v>
       </c>
       <c r="E20" s="3">
-        <v>-251600</v>
+        <v>-246600</v>
       </c>
       <c r="F20" s="3">
-        <v>-15600</v>
+        <v>-15300</v>
       </c>
       <c r="G20" s="3">
-        <v>-256000</v>
+        <v>-250900</v>
       </c>
       <c r="H20" s="3">
-        <v>-54800</v>
+        <v>-53700</v>
       </c>
       <c r="I20" s="3">
-        <v>-138600</v>
+        <v>-135800</v>
       </c>
       <c r="J20" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="K20" s="3">
         <v>-328300</v>
@@ -1302,25 +1302,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>875600</v>
+        <v>858100</v>
       </c>
       <c r="E21" s="3">
-        <v>611200</v>
+        <v>599000</v>
       </c>
       <c r="F21" s="3">
-        <v>1189900</v>
+        <v>1166100</v>
       </c>
       <c r="G21" s="3">
-        <v>784800</v>
+        <v>769100</v>
       </c>
       <c r="H21" s="3">
-        <v>2112600</v>
+        <v>2070400</v>
       </c>
       <c r="I21" s="3">
-        <v>1369400</v>
+        <v>1342000</v>
       </c>
       <c r="J21" s="3">
-        <v>883100</v>
+        <v>865400</v>
       </c>
       <c r="K21" s="3">
         <v>177800</v>
@@ -1352,25 +1352,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>40900</v>
+        <v>40100</v>
       </c>
       <c r="E22" s="3">
-        <v>35100</v>
+        <v>34400</v>
       </c>
       <c r="F22" s="3">
-        <v>35300</v>
+        <v>34600</v>
       </c>
       <c r="G22" s="3">
-        <v>29100</v>
+        <v>28600</v>
       </c>
       <c r="H22" s="3">
-        <v>32500</v>
+        <v>31900</v>
       </c>
       <c r="I22" s="3">
-        <v>39900</v>
+        <v>39100</v>
       </c>
       <c r="J22" s="3">
-        <v>53600</v>
+        <v>52500</v>
       </c>
       <c r="K22" s="3">
         <v>51900</v>
@@ -1402,25 +1402,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>576900</v>
+        <v>565400</v>
       </c>
       <c r="E23" s="3">
-        <v>541300</v>
+        <v>530400</v>
       </c>
       <c r="F23" s="3">
-        <v>979000</v>
+        <v>959400</v>
       </c>
       <c r="G23" s="3">
-        <v>717700</v>
+        <v>703400</v>
       </c>
       <c r="H23" s="3">
-        <v>1873200</v>
+        <v>1835700</v>
       </c>
       <c r="I23" s="3">
-        <v>1291100</v>
+        <v>1265200</v>
       </c>
       <c r="J23" s="3">
-        <v>641900</v>
+        <v>629000</v>
       </c>
       <c r="K23" s="3">
         <v>53600</v>
@@ -1452,25 +1452,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>152800</v>
+        <v>149700</v>
       </c>
       <c r="E24" s="3">
-        <v>179600</v>
+        <v>176000</v>
       </c>
       <c r="F24" s="3">
-        <v>306600</v>
+        <v>300500</v>
       </c>
       <c r="G24" s="3">
-        <v>255900</v>
+        <v>250800</v>
       </c>
       <c r="H24" s="3">
-        <v>493800</v>
+        <v>483900</v>
       </c>
       <c r="I24" s="3">
-        <v>152900</v>
+        <v>149900</v>
       </c>
       <c r="J24" s="3">
-        <v>111700</v>
+        <v>109500</v>
       </c>
       <c r="K24" s="3">
         <v>21600</v>
@@ -1552,25 +1552,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>424200</v>
+        <v>415700</v>
       </c>
       <c r="E26" s="3">
-        <v>361700</v>
+        <v>354500</v>
       </c>
       <c r="F26" s="3">
-        <v>672300</v>
+        <v>658900</v>
       </c>
       <c r="G26" s="3">
-        <v>461800</v>
+        <v>452600</v>
       </c>
       <c r="H26" s="3">
-        <v>1379400</v>
+        <v>1351800</v>
       </c>
       <c r="I26" s="3">
-        <v>1138100</v>
+        <v>1115400</v>
       </c>
       <c r="J26" s="3">
-        <v>530100</v>
+        <v>519500</v>
       </c>
       <c r="K26" s="3">
         <v>32000</v>
@@ -1602,25 +1602,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>404400</v>
+        <v>396300</v>
       </c>
       <c r="E27" s="3">
-        <v>347600</v>
+        <v>340600</v>
       </c>
       <c r="F27" s="3">
-        <v>654600</v>
+        <v>641500</v>
       </c>
       <c r="G27" s="3">
-        <v>447700</v>
+        <v>438800</v>
       </c>
       <c r="H27" s="3">
-        <v>1353100</v>
+        <v>1326000</v>
       </c>
       <c r="I27" s="3">
-        <v>1085600</v>
+        <v>1063900</v>
       </c>
       <c r="J27" s="3">
-        <v>511300</v>
+        <v>501100</v>
       </c>
       <c r="K27" s="3">
         <v>16800</v>
@@ -1852,25 +1852,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-54000</v>
+        <v>-53000</v>
       </c>
       <c r="E32" s="3">
-        <v>251600</v>
+        <v>246600</v>
       </c>
       <c r="F32" s="3">
-        <v>15600</v>
+        <v>15300</v>
       </c>
       <c r="G32" s="3">
-        <v>256000</v>
+        <v>250900</v>
       </c>
       <c r="H32" s="3">
-        <v>54800</v>
+        <v>53700</v>
       </c>
       <c r="I32" s="3">
-        <v>138600</v>
+        <v>135800</v>
       </c>
       <c r="J32" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="K32" s="3">
         <v>328300</v>
@@ -1902,25 +1902,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>404400</v>
+        <v>396300</v>
       </c>
       <c r="E33" s="3">
-        <v>347600</v>
+        <v>340600</v>
       </c>
       <c r="F33" s="3">
-        <v>654600</v>
+        <v>641500</v>
       </c>
       <c r="G33" s="3">
-        <v>447700</v>
+        <v>438800</v>
       </c>
       <c r="H33" s="3">
-        <v>1353100</v>
+        <v>1326000</v>
       </c>
       <c r="I33" s="3">
-        <v>1085600</v>
+        <v>1063900</v>
       </c>
       <c r="J33" s="3">
-        <v>511300</v>
+        <v>501100</v>
       </c>
       <c r="K33" s="3">
         <v>16800</v>
@@ -2002,25 +2002,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>404400</v>
+        <v>396300</v>
       </c>
       <c r="E35" s="3">
-        <v>347600</v>
+        <v>340600</v>
       </c>
       <c r="F35" s="3">
-        <v>654600</v>
+        <v>641500</v>
       </c>
       <c r="G35" s="3">
-        <v>447700</v>
+        <v>438800</v>
       </c>
       <c r="H35" s="3">
-        <v>1353100</v>
+        <v>1326000</v>
       </c>
       <c r="I35" s="3">
-        <v>1085600</v>
+        <v>1063900</v>
       </c>
       <c r="J35" s="3">
-        <v>511300</v>
+        <v>501100</v>
       </c>
       <c r="K35" s="3">
         <v>16800</v>
@@ -2147,25 +2147,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1207200</v>
+        <v>1183100</v>
       </c>
       <c r="E41" s="3">
-        <v>1420600</v>
+        <v>1392200</v>
       </c>
       <c r="F41" s="3">
-        <v>1484500</v>
+        <v>1454800</v>
       </c>
       <c r="G41" s="3">
-        <v>1650300</v>
+        <v>1617300</v>
       </c>
       <c r="H41" s="3">
-        <v>1421800</v>
+        <v>1393300</v>
       </c>
       <c r="I41" s="3">
-        <v>1102700</v>
+        <v>1080600</v>
       </c>
       <c r="J41" s="3">
-        <v>656000</v>
+        <v>642800</v>
       </c>
       <c r="K41" s="3">
         <v>297800</v>
@@ -2247,25 +2247,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>478500</v>
+        <v>468900</v>
       </c>
       <c r="E43" s="3">
-        <v>452400</v>
+        <v>443400</v>
       </c>
       <c r="F43" s="3">
-        <v>486500</v>
+        <v>476700</v>
       </c>
       <c r="G43" s="3">
-        <v>500100</v>
+        <v>490100</v>
       </c>
       <c r="H43" s="3">
-        <v>451400</v>
+        <v>442400</v>
       </c>
       <c r="I43" s="3">
-        <v>384100</v>
+        <v>376400</v>
       </c>
       <c r="J43" s="3">
-        <v>263300</v>
+        <v>258000</v>
       </c>
       <c r="K43" s="3">
         <v>267100</v>
@@ -2297,25 +2297,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1400700</v>
+        <v>1372700</v>
       </c>
       <c r="E44" s="3">
-        <v>1437400</v>
+        <v>1408600</v>
       </c>
       <c r="F44" s="3">
-        <v>1471200</v>
+        <v>1441800</v>
       </c>
       <c r="G44" s="3">
-        <v>1366400</v>
+        <v>1339000</v>
       </c>
       <c r="H44" s="3">
-        <v>1603700</v>
+        <v>1571600</v>
       </c>
       <c r="I44" s="3">
-        <v>1359400</v>
+        <v>1332200</v>
       </c>
       <c r="J44" s="3">
-        <v>916500</v>
+        <v>898200</v>
       </c>
       <c r="K44" s="3">
         <v>821500</v>
@@ -2356,7 +2356,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>15300</v>
+        <v>14900</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -2397,25 +2397,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3086400</v>
+        <v>3024700</v>
       </c>
       <c r="E46" s="3">
-        <v>3310400</v>
+        <v>3244200</v>
       </c>
       <c r="F46" s="3">
-        <v>3442200</v>
+        <v>3373300</v>
       </c>
       <c r="G46" s="3">
-        <v>3532000</v>
+        <v>3461300</v>
       </c>
       <c r="H46" s="3">
-        <v>3476900</v>
+        <v>3407300</v>
       </c>
       <c r="I46" s="3">
-        <v>2846200</v>
+        <v>2789200</v>
       </c>
       <c r="J46" s="3">
-        <v>1835800</v>
+        <v>1799000</v>
       </c>
       <c r="K46" s="3">
         <v>1386400</v>
@@ -2447,25 +2447,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>548000</v>
+        <v>537000</v>
       </c>
       <c r="E47" s="3">
-        <v>505000</v>
+        <v>494900</v>
       </c>
       <c r="F47" s="3">
-        <v>480700</v>
+        <v>471100</v>
       </c>
       <c r="G47" s="3">
-        <v>449200</v>
+        <v>440200</v>
       </c>
       <c r="H47" s="3">
-        <v>402600</v>
+        <v>394500</v>
       </c>
       <c r="I47" s="3">
-        <v>351000</v>
+        <v>344000</v>
       </c>
       <c r="J47" s="3">
-        <v>332900</v>
+        <v>326200</v>
       </c>
       <c r="K47" s="3">
         <v>250200</v>
@@ -2497,25 +2497,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5090300</v>
+        <v>4988400</v>
       </c>
       <c r="E48" s="3">
-        <v>4205200</v>
+        <v>4121100</v>
       </c>
       <c r="F48" s="3">
-        <v>3784800</v>
+        <v>3709100</v>
       </c>
       <c r="G48" s="3">
-        <v>3416800</v>
+        <v>3348400</v>
       </c>
       <c r="H48" s="3">
-        <v>3353100</v>
+        <v>3286000</v>
       </c>
       <c r="I48" s="3">
-        <v>3317600</v>
+        <v>3251200</v>
       </c>
       <c r="J48" s="3">
-        <v>3607700</v>
+        <v>3535500</v>
       </c>
       <c r="K48" s="3">
         <v>3065000</v>
@@ -2547,25 +2547,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>498500</v>
+        <v>488600</v>
       </c>
       <c r="E49" s="3">
-        <v>453400</v>
+        <v>444300</v>
       </c>
       <c r="F49" s="3">
-        <v>435100</v>
+        <v>426400</v>
       </c>
       <c r="G49" s="3">
-        <v>421000</v>
+        <v>412500</v>
       </c>
       <c r="H49" s="3">
-        <v>380100</v>
+        <v>372400</v>
       </c>
       <c r="I49" s="3">
-        <v>390400</v>
+        <v>382600</v>
       </c>
       <c r="J49" s="3">
-        <v>455500</v>
+        <v>446400</v>
       </c>
       <c r="K49" s="3">
         <v>363200</v>
@@ -2697,25 +2697,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>606300</v>
+        <v>594200</v>
       </c>
       <c r="E52" s="3">
-        <v>604100</v>
+        <v>592000</v>
       </c>
       <c r="F52" s="3">
-        <v>497100</v>
+        <v>487100</v>
       </c>
       <c r="G52" s="3">
-        <v>516200</v>
+        <v>505900</v>
       </c>
       <c r="H52" s="3">
-        <v>366300</v>
+        <v>359000</v>
       </c>
       <c r="I52" s="3">
-        <v>400800</v>
+        <v>392800</v>
       </c>
       <c r="J52" s="3">
-        <v>317800</v>
+        <v>311400</v>
       </c>
       <c r="K52" s="3">
         <v>290900</v>
@@ -2797,25 +2797,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9829500</v>
+        <v>9632800</v>
       </c>
       <c r="E54" s="3">
-        <v>9078100</v>
+        <v>8896400</v>
       </c>
       <c r="F54" s="3">
-        <v>8639900</v>
+        <v>8467100</v>
       </c>
       <c r="G54" s="3">
-        <v>8335100</v>
+        <v>8168300</v>
       </c>
       <c r="H54" s="3">
-        <v>7979000</v>
+        <v>7819300</v>
       </c>
       <c r="I54" s="3">
-        <v>7305900</v>
+        <v>7159800</v>
       </c>
       <c r="J54" s="3">
-        <v>6549700</v>
+        <v>6418700</v>
       </c>
       <c r="K54" s="3">
         <v>5355800</v>
@@ -2887,25 +2887,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>837700</v>
+        <v>821000</v>
       </c>
       <c r="E57" s="3">
-        <v>852800</v>
+        <v>835700</v>
       </c>
       <c r="F57" s="3">
-        <v>784100</v>
+        <v>768400</v>
       </c>
       <c r="G57" s="3">
-        <v>826000</v>
+        <v>809500</v>
       </c>
       <c r="H57" s="3">
-        <v>808700</v>
+        <v>792500</v>
       </c>
       <c r="I57" s="3">
-        <v>719500</v>
+        <v>705100</v>
       </c>
       <c r="J57" s="3">
-        <v>643900</v>
+        <v>631000</v>
       </c>
       <c r="K57" s="3">
         <v>607600</v>
@@ -2937,25 +2937,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18300</v>
+        <v>17900</v>
       </c>
       <c r="E58" s="3">
-        <v>12700</v>
+        <v>12400</v>
       </c>
       <c r="F58" s="3">
-        <v>12700</v>
+        <v>12500</v>
       </c>
       <c r="G58" s="3">
-        <v>11500</v>
+        <v>11300</v>
       </c>
       <c r="H58" s="3">
-        <v>362500</v>
+        <v>355300</v>
       </c>
       <c r="I58" s="3">
-        <v>53900</v>
+        <v>52800</v>
       </c>
       <c r="J58" s="3">
-        <v>74900</v>
+        <v>73400</v>
       </c>
       <c r="K58" s="3">
         <v>7900</v>
@@ -2987,25 +2987,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>125800</v>
+        <v>123300</v>
       </c>
       <c r="E59" s="3">
-        <v>236100</v>
+        <v>231300</v>
       </c>
       <c r="F59" s="3">
-        <v>227100</v>
+        <v>222600</v>
       </c>
       <c r="G59" s="3">
-        <v>281600</v>
+        <v>275900</v>
       </c>
       <c r="H59" s="3">
-        <v>100800</v>
+        <v>98800</v>
       </c>
       <c r="I59" s="3">
-        <v>179300</v>
+        <v>175700</v>
       </c>
       <c r="J59" s="3">
-        <v>215900</v>
+        <v>211600</v>
       </c>
       <c r="K59" s="3">
         <v>143700</v>
@@ -3037,25 +3037,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>981800</v>
+        <v>962200</v>
       </c>
       <c r="E60" s="3">
-        <v>1101500</v>
+        <v>1079500</v>
       </c>
       <c r="F60" s="3">
-        <v>1024000</v>
+        <v>1003500</v>
       </c>
       <c r="G60" s="3">
-        <v>1119100</v>
+        <v>1096700</v>
       </c>
       <c r="H60" s="3">
-        <v>1272000</v>
+        <v>1246500</v>
       </c>
       <c r="I60" s="3">
-        <v>952700</v>
+        <v>933600</v>
       </c>
       <c r="J60" s="3">
-        <v>934700</v>
+        <v>916000</v>
       </c>
       <c r="K60" s="3">
         <v>759200</v>
@@ -3087,25 +3087,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1395600</v>
+        <v>1367700</v>
       </c>
       <c r="E61" s="3">
-        <v>1242900</v>
+        <v>1218000</v>
       </c>
       <c r="F61" s="3">
-        <v>1144700</v>
+        <v>1121800</v>
       </c>
       <c r="G61" s="3">
-        <v>1109600</v>
+        <v>1087400</v>
       </c>
       <c r="H61" s="3">
-        <v>589500</v>
+        <v>577700</v>
       </c>
       <c r="I61" s="3">
-        <v>965400</v>
+        <v>946100</v>
       </c>
       <c r="J61" s="3">
-        <v>1380000</v>
+        <v>1352400</v>
       </c>
       <c r="K61" s="3">
         <v>1270200</v>
@@ -3137,25 +3137,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1995100</v>
+        <v>1955200</v>
       </c>
       <c r="E62" s="3">
-        <v>1775700</v>
+        <v>1740200</v>
       </c>
       <c r="F62" s="3">
-        <v>1603000</v>
+        <v>1570900</v>
       </c>
       <c r="G62" s="3">
-        <v>1674700</v>
+        <v>1641200</v>
       </c>
       <c r="H62" s="3">
-        <v>1577100</v>
+        <v>1545600</v>
       </c>
       <c r="I62" s="3">
-        <v>1535200</v>
+        <v>1504500</v>
       </c>
       <c r="J62" s="3">
-        <v>1727700</v>
+        <v>1693100</v>
       </c>
       <c r="K62" s="3">
         <v>1676400</v>
@@ -3337,25 +3337,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4545500</v>
+        <v>4454500</v>
       </c>
       <c r="E66" s="3">
-        <v>4278300</v>
+        <v>4192700</v>
       </c>
       <c r="F66" s="3">
-        <v>3928800</v>
+        <v>3850200</v>
       </c>
       <c r="G66" s="3">
-        <v>4009800</v>
+        <v>3929600</v>
       </c>
       <c r="H66" s="3">
-        <v>3510900</v>
+        <v>3440600</v>
       </c>
       <c r="I66" s="3">
-        <v>3575100</v>
+        <v>3503600</v>
       </c>
       <c r="J66" s="3">
-        <v>4118100</v>
+        <v>4035800</v>
       </c>
       <c r="K66" s="3">
         <v>3783500</v>
@@ -3607,25 +3607,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4104700</v>
+        <v>4022600</v>
       </c>
       <c r="E72" s="3">
-        <v>3620400</v>
+        <v>3548000</v>
       </c>
       <c r="F72" s="3">
-        <v>2278700</v>
+        <v>2233100</v>
       </c>
       <c r="G72" s="3">
-        <v>3146000</v>
+        <v>3083100</v>
       </c>
       <c r="H72" s="3">
-        <v>1623200</v>
+        <v>1590800</v>
       </c>
       <c r="I72" s="3">
-        <v>2088200</v>
+        <v>2046500</v>
       </c>
       <c r="J72" s="3">
-        <v>216300</v>
+        <v>212000</v>
       </c>
       <c r="K72" s="3">
         <v>-582400</v>
@@ -3807,25 +3807,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5284000</v>
+        <v>5178300</v>
       </c>
       <c r="E76" s="3">
-        <v>4799700</v>
+        <v>4703700</v>
       </c>
       <c r="F76" s="3">
-        <v>4711100</v>
+        <v>4616800</v>
       </c>
       <c r="G76" s="3">
-        <v>4325300</v>
+        <v>4238800</v>
       </c>
       <c r="H76" s="3">
-        <v>4468100</v>
+        <v>4378700</v>
       </c>
       <c r="I76" s="3">
-        <v>3730800</v>
+        <v>3656200</v>
       </c>
       <c r="J76" s="3">
-        <v>2431600</v>
+        <v>2382900</v>
       </c>
       <c r="K76" s="3">
         <v>1572200</v>
@@ -3962,25 +3962,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>404400</v>
+        <v>396300</v>
       </c>
       <c r="E81" s="3">
-        <v>347600</v>
+        <v>340600</v>
       </c>
       <c r="F81" s="3">
-        <v>654600</v>
+        <v>641500</v>
       </c>
       <c r="G81" s="3">
-        <v>447700</v>
+        <v>438800</v>
       </c>
       <c r="H81" s="3">
-        <v>1353100</v>
+        <v>1326000</v>
       </c>
       <c r="I81" s="3">
-        <v>1085600</v>
+        <v>1063900</v>
       </c>
       <c r="J81" s="3">
-        <v>511300</v>
+        <v>501100</v>
       </c>
       <c r="K81" s="3">
         <v>16800</v>
@@ -4332,25 +4332,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>269300</v>
+        <v>263900</v>
       </c>
       <c r="E89" s="3">
-        <v>607700</v>
+        <v>595500</v>
       </c>
       <c r="F89" s="3">
-        <v>239100</v>
+        <v>234300</v>
       </c>
       <c r="G89" s="3">
-        <v>1032900</v>
+        <v>1012300</v>
       </c>
       <c r="H89" s="3">
-        <v>724400</v>
+        <v>709900</v>
       </c>
       <c r="I89" s="3">
-        <v>695300</v>
+        <v>681300</v>
       </c>
       <c r="J89" s="3">
-        <v>783800</v>
+        <v>768200</v>
       </c>
       <c r="K89" s="3">
         <v>431200</v>
@@ -4552,25 +4552,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-565400</v>
+        <v>-554100</v>
       </c>
       <c r="E94" s="3">
-        <v>-536600</v>
+        <v>-525900</v>
       </c>
       <c r="F94" s="3">
-        <v>-409900</v>
+        <v>-401700</v>
       </c>
       <c r="G94" s="3">
-        <v>-476500</v>
+        <v>-466900</v>
       </c>
       <c r="H94" s="3">
-        <v>-317200</v>
+        <v>-310800</v>
       </c>
       <c r="I94" s="3">
-        <v>-276400</v>
+        <v>-270900</v>
       </c>
       <c r="J94" s="3">
-        <v>-265000</v>
+        <v>-259700</v>
       </c>
       <c r="K94" s="3">
         <v>-269800</v>
@@ -4822,25 +4822,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="E100" s="3">
-        <v>-186500</v>
+        <v>-182800</v>
       </c>
       <c r="F100" s="3">
-        <v>-4000</v>
+        <v>-3900</v>
       </c>
       <c r="G100" s="3">
-        <v>-370200</v>
+        <v>-362800</v>
       </c>
       <c r="H100" s="3">
-        <v>-84400</v>
+        <v>-82700</v>
       </c>
       <c r="I100" s="3">
-        <v>44900</v>
+        <v>44000</v>
       </c>
       <c r="J100" s="3">
-        <v>-167100</v>
+        <v>-163800</v>
       </c>
       <c r="K100" s="3">
         <v>-188000</v>
@@ -4872,22 +4872,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>84000</v>
+        <v>82300</v>
       </c>
       <c r="E101" s="3">
-        <v>51600</v>
+        <v>50600</v>
       </c>
       <c r="F101" s="3">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G101" s="3">
-        <v>42300</v>
+        <v>41400</v>
       </c>
       <c r="H101" s="3">
-        <v>-3700</v>
+        <v>-3600</v>
       </c>
       <c r="I101" s="3">
-        <v>-17000</v>
+        <v>-16700</v>
       </c>
       <c r="J101" s="3">
         <v>-1900</v>
@@ -4922,25 +4922,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-213400</v>
+        <v>-209100</v>
       </c>
       <c r="E102" s="3">
-        <v>-63900</v>
+        <v>-62600</v>
       </c>
       <c r="F102" s="3">
-        <v>-165800</v>
+        <v>-162500</v>
       </c>
       <c r="G102" s="3">
-        <v>228500</v>
+        <v>224000</v>
       </c>
       <c r="H102" s="3">
-        <v>319100</v>
+        <v>312700</v>
       </c>
       <c r="I102" s="3">
-        <v>446700</v>
+        <v>437800</v>
       </c>
       <c r="J102" s="3">
-        <v>349800</v>
+        <v>342800</v>
       </c>
       <c r="K102" s="3">
         <v>-20200</v>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -656,241 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3233700</v>
+        <v>2890600</v>
       </c>
       <c r="E8" s="3">
-        <v>3625700</v>
+        <v>3296100</v>
       </c>
       <c r="F8" s="3">
-        <v>3757500</v>
+        <v>3695600</v>
       </c>
       <c r="G8" s="3">
-        <v>4390800</v>
+        <v>3830000</v>
       </c>
       <c r="H8" s="3">
-        <v>4802600</v>
+        <v>4475600</v>
       </c>
       <c r="I8" s="3">
-        <v>3864000</v>
+        <v>4895200</v>
       </c>
       <c r="J8" s="3">
+        <v>3938600</v>
+      </c>
+      <c r="K8" s="3">
         <v>2937400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2617200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1267800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1661200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1587400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1755800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1279600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>945000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>840400</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2683400</v>
+        <v>2751300</v>
       </c>
       <c r="E9" s="3">
-        <v>2789000</v>
+        <v>2735200</v>
       </c>
       <c r="F9" s="3">
-        <v>2734600</v>
+        <v>2842800</v>
       </c>
       <c r="G9" s="3">
-        <v>3119400</v>
+        <v>2787300</v>
       </c>
       <c r="H9" s="3">
-        <v>2861300</v>
+        <v>3179600</v>
       </c>
       <c r="I9" s="3">
-        <v>2324600</v>
+        <v>2916500</v>
       </c>
       <c r="J9" s="3">
+        <v>2369400</v>
+      </c>
+      <c r="K9" s="3">
         <v>2220700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2121800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1276900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1583900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1516400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1573800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1242100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>788400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>658500</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>550300</v>
+        <v>139300</v>
       </c>
       <c r="E10" s="3">
-        <v>836600</v>
+        <v>560900</v>
       </c>
       <c r="F10" s="3">
-        <v>1023000</v>
+        <v>852800</v>
       </c>
       <c r="G10" s="3">
-        <v>1271400</v>
+        <v>1042700</v>
       </c>
       <c r="H10" s="3">
-        <v>1941300</v>
+        <v>1296000</v>
       </c>
       <c r="I10" s="3">
-        <v>1539500</v>
+        <v>1978700</v>
       </c>
       <c r="J10" s="3">
+        <v>1569200</v>
+      </c>
+      <c r="K10" s="3">
         <v>716700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>495400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-9100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>182100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>37500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>156700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>181900</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +921,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,11 +969,14 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1009,58 +1025,64 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4500</v>
+        <v>2592000</v>
       </c>
       <c r="E14" s="3">
-        <v>19500</v>
+        <v>-4600</v>
       </c>
       <c r="F14" s="3">
-        <v>7700</v>
+        <v>19900</v>
       </c>
       <c r="G14" s="3">
-        <v>284100</v>
+        <v>7800</v>
       </c>
       <c r="H14" s="3">
+        <v>289600</v>
+      </c>
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
-        <v>87800</v>
-      </c>
       <c r="J14" s="3">
+        <v>89500</v>
+      </c>
+      <c r="K14" s="3">
         <v>22000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>51000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>201200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>154400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>222800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-81400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1109,8 +1131,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1126,108 +1151,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2681200</v>
+        <v>5347100</v>
       </c>
       <c r="E17" s="3">
-        <v>2814200</v>
+        <v>2732900</v>
       </c>
       <c r="F17" s="3">
-        <v>2748300</v>
+        <v>2868500</v>
       </c>
       <c r="G17" s="3">
-        <v>3408000</v>
+        <v>2801300</v>
       </c>
       <c r="H17" s="3">
-        <v>2881400</v>
+        <v>3473800</v>
       </c>
       <c r="I17" s="3">
-        <v>2423900</v>
+        <v>2936900</v>
       </c>
       <c r="J17" s="3">
+        <v>2470600</v>
+      </c>
+      <c r="K17" s="3">
         <v>2258600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2183400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1270700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1795300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1548400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1735800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1472600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>727500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>552500</v>
+        <v>-2456600</v>
       </c>
       <c r="E18" s="3">
-        <v>811500</v>
+        <v>563200</v>
       </c>
       <c r="F18" s="3">
-        <v>1009300</v>
+        <v>827100</v>
       </c>
       <c r="G18" s="3">
-        <v>982800</v>
+        <v>1028800</v>
       </c>
       <c r="H18" s="3">
-        <v>1921200</v>
+        <v>1001800</v>
       </c>
       <c r="I18" s="3">
-        <v>1440100</v>
+        <v>1958300</v>
       </c>
       <c r="J18" s="3">
+        <v>1467900</v>
+      </c>
+      <c r="K18" s="3">
         <v>678900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>433800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-134100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-193000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>217600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>118500</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1246,258 +1278,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>53000</v>
+        <v>-242300</v>
       </c>
       <c r="E20" s="3">
-        <v>-246600</v>
+        <v>54000</v>
       </c>
       <c r="F20" s="3">
-        <v>-15300</v>
+        <v>-251400</v>
       </c>
       <c r="G20" s="3">
-        <v>-250900</v>
+        <v>-15600</v>
       </c>
       <c r="H20" s="3">
-        <v>-53700</v>
+        <v>-255700</v>
       </c>
       <c r="I20" s="3">
-        <v>-135800</v>
+        <v>-54700</v>
       </c>
       <c r="J20" s="3">
+        <v>-138400</v>
+      </c>
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-328300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-74600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>104800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-85200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-76400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>858100</v>
+        <v>-2668900</v>
       </c>
       <c r="E21" s="3">
-        <v>599000</v>
+        <v>874600</v>
       </c>
       <c r="F21" s="3">
-        <v>1166100</v>
+        <v>610500</v>
       </c>
       <c r="G21" s="3">
-        <v>769100</v>
+        <v>1188600</v>
       </c>
       <c r="H21" s="3">
-        <v>2070400</v>
+        <v>784000</v>
       </c>
       <c r="I21" s="3">
-        <v>1342000</v>
+        <v>2110300</v>
       </c>
       <c r="J21" s="3">
+        <v>1367900</v>
+      </c>
+      <c r="K21" s="3">
         <v>865400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>177800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>80100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>281500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-103100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>217300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>40100</v>
+        <v>45900</v>
       </c>
       <c r="E22" s="3">
-        <v>34400</v>
+        <v>40900</v>
       </c>
       <c r="F22" s="3">
-        <v>34600</v>
+        <v>35100</v>
       </c>
       <c r="G22" s="3">
-        <v>28600</v>
+        <v>35300</v>
       </c>
       <c r="H22" s="3">
-        <v>31900</v>
+        <v>29100</v>
       </c>
       <c r="I22" s="3">
-        <v>39100</v>
+        <v>32500</v>
       </c>
       <c r="J22" s="3">
+        <v>39900</v>
+      </c>
+      <c r="K22" s="3">
         <v>52500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>70100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>65200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>78000</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>565400</v>
+        <v>-2744700</v>
       </c>
       <c r="E23" s="3">
-        <v>530400</v>
+        <v>576300</v>
       </c>
       <c r="F23" s="3">
-        <v>959400</v>
+        <v>540700</v>
       </c>
       <c r="G23" s="3">
-        <v>703400</v>
+        <v>977900</v>
       </c>
       <c r="H23" s="3">
-        <v>1835700</v>
+        <v>716900</v>
       </c>
       <c r="I23" s="3">
-        <v>1265200</v>
+        <v>1871100</v>
       </c>
       <c r="J23" s="3">
+        <v>1289600</v>
+      </c>
+      <c r="K23" s="3">
         <v>629000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>53600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-124600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-99400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-142300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-347400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>208700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>149700</v>
+        <v>-284100</v>
       </c>
       <c r="E24" s="3">
-        <v>176000</v>
+        <v>152600</v>
       </c>
       <c r="F24" s="3">
-        <v>300500</v>
+        <v>179400</v>
       </c>
       <c r="G24" s="3">
-        <v>250800</v>
+        <v>306300</v>
       </c>
       <c r="H24" s="3">
-        <v>483900</v>
+        <v>255600</v>
       </c>
       <c r="I24" s="3">
-        <v>149900</v>
+        <v>493300</v>
       </c>
       <c r="J24" s="3">
+        <v>152800</v>
+      </c>
+      <c r="K24" s="3">
         <v>109500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-115400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>62100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-166600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1546,108 +1594,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>415700</v>
+        <v>-2460700</v>
       </c>
       <c r="E26" s="3">
-        <v>354500</v>
+        <v>423700</v>
       </c>
       <c r="F26" s="3">
-        <v>658900</v>
+        <v>361300</v>
       </c>
       <c r="G26" s="3">
-        <v>452600</v>
+        <v>671600</v>
       </c>
       <c r="H26" s="3">
-        <v>1351800</v>
+        <v>461300</v>
       </c>
       <c r="I26" s="3">
-        <v>1115400</v>
+        <v>1377900</v>
       </c>
       <c r="J26" s="3">
+        <v>1136900</v>
+      </c>
+      <c r="K26" s="3">
         <v>519500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-161400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-319800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>168900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>396300</v>
+        <v>-2459500</v>
       </c>
       <c r="E27" s="3">
-        <v>340600</v>
+        <v>404000</v>
       </c>
       <c r="F27" s="3">
-        <v>641500</v>
+        <v>347200</v>
       </c>
       <c r="G27" s="3">
-        <v>438800</v>
+        <v>653900</v>
       </c>
       <c r="H27" s="3">
-        <v>1326000</v>
+        <v>447200</v>
       </c>
       <c r="I27" s="3">
-        <v>1063900</v>
+        <v>1351600</v>
       </c>
       <c r="J27" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="K27" s="3">
         <v>501100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-160000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-319800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>179500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1696,8 +1753,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1746,8 +1806,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1796,8 +1859,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1846,108 +1912,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-53000</v>
+        <v>242300</v>
       </c>
       <c r="E32" s="3">
-        <v>246600</v>
+        <v>-54000</v>
       </c>
       <c r="F32" s="3">
-        <v>15300</v>
+        <v>251400</v>
       </c>
       <c r="G32" s="3">
-        <v>250900</v>
+        <v>15600</v>
       </c>
       <c r="H32" s="3">
-        <v>53700</v>
+        <v>255700</v>
       </c>
       <c r="I32" s="3">
-        <v>135800</v>
+        <v>54700</v>
       </c>
       <c r="J32" s="3">
+        <v>138400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>328300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>74600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-104800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>85200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>76400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>396300</v>
+        <v>-2459500</v>
       </c>
       <c r="E33" s="3">
-        <v>340600</v>
+        <v>404000</v>
       </c>
       <c r="F33" s="3">
-        <v>641500</v>
+        <v>347200</v>
       </c>
       <c r="G33" s="3">
-        <v>438800</v>
+        <v>653900</v>
       </c>
       <c r="H33" s="3">
-        <v>1326000</v>
+        <v>447200</v>
       </c>
       <c r="I33" s="3">
-        <v>1063900</v>
+        <v>1351600</v>
       </c>
       <c r="J33" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="K33" s="3">
         <v>501100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-160000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-319800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>179500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1996,113 +2071,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>396300</v>
+        <v>-2459500</v>
       </c>
       <c r="E35" s="3">
-        <v>340600</v>
+        <v>404000</v>
       </c>
       <c r="F35" s="3">
-        <v>641500</v>
+        <v>347200</v>
       </c>
       <c r="G35" s="3">
-        <v>438800</v>
+        <v>653900</v>
       </c>
       <c r="H35" s="3">
-        <v>1326000</v>
+        <v>447200</v>
       </c>
       <c r="I35" s="3">
-        <v>1063900</v>
+        <v>1351600</v>
       </c>
       <c r="J35" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="K35" s="3">
         <v>501100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-160000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-319800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>179500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2121,8 +2205,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2141,58 +2226,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1183100</v>
+        <v>1391000</v>
       </c>
       <c r="E41" s="3">
-        <v>1392200</v>
+        <v>1205900</v>
       </c>
       <c r="F41" s="3">
-        <v>1454800</v>
+        <v>1419100</v>
       </c>
       <c r="G41" s="3">
-        <v>1617300</v>
+        <v>1482800</v>
       </c>
       <c r="H41" s="3">
-        <v>1393300</v>
+        <v>1648500</v>
       </c>
       <c r="I41" s="3">
-        <v>1080600</v>
+        <v>1420200</v>
       </c>
       <c r="J41" s="3">
+        <v>1101400</v>
+      </c>
+      <c r="K41" s="3">
         <v>642800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>297800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>321300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>158300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>139400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>434300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>55300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2241,125 +2330,134 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>468900</v>
+        <v>538700</v>
       </c>
       <c r="E43" s="3">
-        <v>443400</v>
+        <v>478000</v>
       </c>
       <c r="F43" s="3">
-        <v>476700</v>
+        <v>451900</v>
       </c>
       <c r="G43" s="3">
-        <v>490100</v>
+        <v>485900</v>
       </c>
       <c r="H43" s="3">
-        <v>442400</v>
+        <v>499500</v>
       </c>
       <c r="I43" s="3">
-        <v>376400</v>
+        <v>450900</v>
       </c>
       <c r="J43" s="3">
+        <v>383700</v>
+      </c>
+      <c r="K43" s="3">
         <v>258000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>267100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>295100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>456600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>434600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>422000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>389000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>346200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1372700</v>
+        <v>1434700</v>
       </c>
       <c r="E44" s="3">
-        <v>1408600</v>
+        <v>1399100</v>
       </c>
       <c r="F44" s="3">
-        <v>1441800</v>
+        <v>1435800</v>
       </c>
       <c r="G44" s="3">
-        <v>1339000</v>
+        <v>1469600</v>
       </c>
       <c r="H44" s="3">
-        <v>1571600</v>
+        <v>1364900</v>
       </c>
       <c r="I44" s="3">
-        <v>1332200</v>
+        <v>1602000</v>
       </c>
       <c r="J44" s="3">
+        <v>1357900</v>
+      </c>
+      <c r="K44" s="3">
         <v>898200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>821500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>765500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>328900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>281200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>232000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>197200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>38700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>15200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -2370,229 +2468,244 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>6500</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>84300</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3" t="s">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3024700</v>
+        <v>3364400</v>
       </c>
       <c r="E46" s="3">
-        <v>3244200</v>
+        <v>3083000</v>
       </c>
       <c r="F46" s="3">
-        <v>3373300</v>
+        <v>3306800</v>
       </c>
       <c r="G46" s="3">
-        <v>3461300</v>
+        <v>3438400</v>
       </c>
       <c r="H46" s="3">
-        <v>3407300</v>
+        <v>3528100</v>
       </c>
       <c r="I46" s="3">
-        <v>2789200</v>
+        <v>3473100</v>
       </c>
       <c r="J46" s="3">
+        <v>2843000</v>
+      </c>
+      <c r="K46" s="3">
         <v>1799000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1386400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1388400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>943800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>939500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>789700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1020500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>440200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>203200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>537000</v>
+        <v>417500</v>
       </c>
       <c r="E47" s="3">
-        <v>494900</v>
+        <v>547400</v>
       </c>
       <c r="F47" s="3">
-        <v>471100</v>
+        <v>504400</v>
       </c>
       <c r="G47" s="3">
-        <v>440200</v>
+        <v>480200</v>
       </c>
       <c r="H47" s="3">
-        <v>394500</v>
+        <v>448700</v>
       </c>
       <c r="I47" s="3">
-        <v>344000</v>
+        <v>402100</v>
       </c>
       <c r="J47" s="3">
+        <v>350600</v>
+      </c>
+      <c r="K47" s="3">
         <v>326200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>250200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>242700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>251400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>197500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>166300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>174400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>143600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4988400</v>
+        <v>3368500</v>
       </c>
       <c r="E48" s="3">
-        <v>4121100</v>
+        <v>5084700</v>
       </c>
       <c r="F48" s="3">
-        <v>3709100</v>
+        <v>4200600</v>
       </c>
       <c r="G48" s="3">
-        <v>3348400</v>
+        <v>3780700</v>
       </c>
       <c r="H48" s="3">
-        <v>3286000</v>
+        <v>3413000</v>
       </c>
       <c r="I48" s="3">
-        <v>3251200</v>
+        <v>3349400</v>
       </c>
       <c r="J48" s="3">
+        <v>3313900</v>
+      </c>
+      <c r="K48" s="3">
         <v>3535500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3065000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3057100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3388600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3532300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3384000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3620500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1556800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1326500</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>488600</v>
+        <v>27300</v>
       </c>
       <c r="E49" s="3">
-        <v>444300</v>
+        <v>498000</v>
       </c>
       <c r="F49" s="3">
-        <v>426400</v>
+        <v>452900</v>
       </c>
       <c r="G49" s="3">
-        <v>412500</v>
+        <v>434700</v>
       </c>
       <c r="H49" s="3">
-        <v>372400</v>
+        <v>420500</v>
       </c>
       <c r="I49" s="3">
-        <v>382600</v>
+        <v>379600</v>
       </c>
       <c r="J49" s="3">
+        <v>389900</v>
+      </c>
+      <c r="K49" s="3">
         <v>446400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>363200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>371400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>427900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>465500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>420700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>453400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>53500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2641,8 +2754,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2691,58 +2807,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>594200</v>
+        <v>601200</v>
       </c>
       <c r="E52" s="3">
-        <v>592000</v>
+        <v>605600</v>
       </c>
       <c r="F52" s="3">
-        <v>487100</v>
+        <v>603400</v>
       </c>
       <c r="G52" s="3">
-        <v>505900</v>
+        <v>496500</v>
       </c>
       <c r="H52" s="3">
-        <v>359000</v>
+        <v>515600</v>
       </c>
       <c r="I52" s="3">
-        <v>392800</v>
+        <v>365900</v>
       </c>
       <c r="J52" s="3">
+        <v>400400</v>
+      </c>
+      <c r="K52" s="3">
         <v>311400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>290900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>273300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>262800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>248400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>243300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>227000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>190200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>159700</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2791,58 +2913,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9632800</v>
+        <v>7778800</v>
       </c>
       <c r="E54" s="3">
-        <v>8896400</v>
+        <v>9818700</v>
       </c>
       <c r="F54" s="3">
-        <v>8467100</v>
+        <v>9068100</v>
       </c>
       <c r="G54" s="3">
-        <v>8168300</v>
+        <v>8630400</v>
       </c>
       <c r="H54" s="3">
-        <v>7819300</v>
+        <v>8325900</v>
       </c>
       <c r="I54" s="3">
-        <v>7159800</v>
+        <v>7970200</v>
       </c>
       <c r="J54" s="3">
+        <v>7297900</v>
+      </c>
+      <c r="K54" s="3">
         <v>6418700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5355800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5332800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5274600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5383200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5004000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5495800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2384400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1876100</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2861,8 +2989,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2881,308 +3010,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>821000</v>
+        <v>896000</v>
       </c>
       <c r="E57" s="3">
-        <v>835700</v>
+        <v>836800</v>
       </c>
       <c r="F57" s="3">
-        <v>768400</v>
+        <v>851800</v>
       </c>
       <c r="G57" s="3">
-        <v>809500</v>
+        <v>783200</v>
       </c>
       <c r="H57" s="3">
-        <v>792500</v>
+        <v>825100</v>
       </c>
       <c r="I57" s="3">
-        <v>705100</v>
+        <v>807800</v>
       </c>
       <c r="J57" s="3">
+        <v>718700</v>
+      </c>
+      <c r="K57" s="3">
         <v>631000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>607600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>598600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>488000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>453700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>440100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>476300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>296100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>221800</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17900</v>
+        <v>853300</v>
       </c>
       <c r="E58" s="3">
-        <v>12400</v>
+        <v>18200</v>
       </c>
       <c r="F58" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="G58" s="3">
-        <v>11300</v>
+        <v>12700</v>
       </c>
       <c r="H58" s="3">
-        <v>355300</v>
+        <v>11500</v>
       </c>
       <c r="I58" s="3">
-        <v>52800</v>
+        <v>362100</v>
       </c>
       <c r="J58" s="3">
+        <v>53800</v>
+      </c>
+      <c r="K58" s="3">
         <v>73400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>298800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>384300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>22200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>109000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>504100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>43000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>123300</v>
+        <v>232000</v>
       </c>
       <c r="E59" s="3">
-        <v>231300</v>
+        <v>125700</v>
       </c>
       <c r="F59" s="3">
-        <v>222600</v>
+        <v>235800</v>
       </c>
       <c r="G59" s="3">
-        <v>275900</v>
+        <v>226900</v>
       </c>
       <c r="H59" s="3">
-        <v>98800</v>
+        <v>281200</v>
       </c>
       <c r="I59" s="3">
-        <v>175700</v>
+        <v>100700</v>
       </c>
       <c r="J59" s="3">
+        <v>179100</v>
+      </c>
+      <c r="K59" s="3">
         <v>211600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>143700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>199200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>36500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>962200</v>
+        <v>1981300</v>
       </c>
       <c r="E60" s="3">
-        <v>1079500</v>
+        <v>980800</v>
       </c>
       <c r="F60" s="3">
-        <v>1003500</v>
+        <v>1100300</v>
       </c>
       <c r="G60" s="3">
-        <v>1096700</v>
+        <v>1022800</v>
       </c>
       <c r="H60" s="3">
-        <v>1246500</v>
+        <v>1117800</v>
       </c>
       <c r="I60" s="3">
-        <v>933600</v>
+        <v>1270600</v>
       </c>
       <c r="J60" s="3">
+        <v>951600</v>
+      </c>
+      <c r="K60" s="3">
         <v>916000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>759200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1096600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>908800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>507900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>555000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>989700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>357600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>466900</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1367700</v>
+        <v>1378500</v>
       </c>
       <c r="E61" s="3">
-        <v>1218000</v>
+        <v>1394100</v>
       </c>
       <c r="F61" s="3">
-        <v>1121800</v>
+        <v>1241500</v>
       </c>
       <c r="G61" s="3">
-        <v>1087400</v>
+        <v>1143500</v>
       </c>
       <c r="H61" s="3">
-        <v>577700</v>
+        <v>1108400</v>
       </c>
       <c r="I61" s="3">
-        <v>946100</v>
+        <v>588900</v>
       </c>
       <c r="J61" s="3">
+        <v>964300</v>
+      </c>
+      <c r="K61" s="3">
         <v>1352400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1270200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1181600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1137600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1882700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1578200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1507200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>469900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1955200</v>
+        <v>1610700</v>
       </c>
       <c r="E62" s="3">
-        <v>1740200</v>
+        <v>1992900</v>
       </c>
       <c r="F62" s="3">
-        <v>1570900</v>
+        <v>1773800</v>
       </c>
       <c r="G62" s="3">
-        <v>1641200</v>
+        <v>1601300</v>
       </c>
       <c r="H62" s="3">
-        <v>1545600</v>
+        <v>1672900</v>
       </c>
       <c r="I62" s="3">
-        <v>1504500</v>
+        <v>1575400</v>
       </c>
       <c r="J62" s="3">
+        <v>1533500</v>
+      </c>
+      <c r="K62" s="3">
         <v>1693100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1676400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1424800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1692500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1298800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1292200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1396700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>615700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3231,8 +3379,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3281,8 +3432,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3331,58 +3485,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4454500</v>
+        <v>5127000</v>
       </c>
       <c r="E66" s="3">
-        <v>4192700</v>
+        <v>4540500</v>
       </c>
       <c r="F66" s="3">
-        <v>3850200</v>
+        <v>4273600</v>
       </c>
       <c r="G66" s="3">
-        <v>3929600</v>
+        <v>3924500</v>
       </c>
       <c r="H66" s="3">
-        <v>3440600</v>
+        <v>4005400</v>
       </c>
       <c r="I66" s="3">
-        <v>3503600</v>
+        <v>3507000</v>
       </c>
       <c r="J66" s="3">
+        <v>3571200</v>
+      </c>
+      <c r="K66" s="3">
         <v>4035800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3783500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3770300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3797100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3690800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3426700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3894700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1444200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1047600</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3401,8 +3561,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3451,8 +3612,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3501,8 +3665,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3551,8 +3718,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3601,58 +3771,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4022600</v>
+        <v>1473900</v>
       </c>
       <c r="E72" s="3">
-        <v>3548000</v>
+        <v>4100200</v>
       </c>
       <c r="F72" s="3">
-        <v>2233100</v>
+        <v>3616400</v>
       </c>
       <c r="G72" s="3">
-        <v>3083100</v>
+        <v>2276200</v>
       </c>
       <c r="H72" s="3">
-        <v>1590800</v>
+        <v>3142500</v>
       </c>
       <c r="I72" s="3">
-        <v>2046500</v>
+        <v>1621400</v>
       </c>
       <c r="J72" s="3">
+        <v>2085900</v>
+      </c>
+      <c r="K72" s="3">
         <v>212000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-582400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-628000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-675700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-609100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-703100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-709000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-301900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-413700</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3701,8 +3877,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3751,8 +3930,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3801,58 +3983,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5178300</v>
+        <v>2651900</v>
       </c>
       <c r="E76" s="3">
-        <v>4703700</v>
+        <v>5278200</v>
       </c>
       <c r="F76" s="3">
-        <v>4616800</v>
+        <v>4794500</v>
       </c>
       <c r="G76" s="3">
-        <v>4238800</v>
+        <v>4705900</v>
       </c>
       <c r="H76" s="3">
-        <v>4378700</v>
+        <v>4320600</v>
       </c>
       <c r="I76" s="3">
-        <v>3656200</v>
+        <v>4463200</v>
       </c>
       <c r="J76" s="3">
+        <v>3726700</v>
+      </c>
+      <c r="K76" s="3">
         <v>2382900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1572200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1562500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1477500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1692400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1577300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1601100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>940200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3901,113 +4089,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>396300</v>
+        <v>-2459500</v>
       </c>
       <c r="E81" s="3">
-        <v>340600</v>
+        <v>404000</v>
       </c>
       <c r="F81" s="3">
-        <v>641500</v>
+        <v>347200</v>
       </c>
       <c r="G81" s="3">
-        <v>438800</v>
+        <v>653900</v>
       </c>
       <c r="H81" s="3">
-        <v>1326000</v>
+        <v>447200</v>
       </c>
       <c r="I81" s="3">
-        <v>1063900</v>
+        <v>1351600</v>
       </c>
       <c r="J81" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="K81" s="3">
         <v>501100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-160000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-319800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>179500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4026,8 +4223,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4076,8 +4274,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4126,8 +4327,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4176,8 +4380,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4226,8 +4433,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4276,8 +4486,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4326,58 +4539,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>263900</v>
+        <v>117100</v>
       </c>
       <c r="E89" s="3">
-        <v>595500</v>
+        <v>269000</v>
       </c>
       <c r="F89" s="3">
-        <v>234300</v>
+        <v>607000</v>
       </c>
       <c r="G89" s="3">
-        <v>1012300</v>
+        <v>238800</v>
       </c>
       <c r="H89" s="3">
-        <v>709900</v>
+        <v>1031800</v>
       </c>
       <c r="I89" s="3">
-        <v>681300</v>
+        <v>723600</v>
       </c>
       <c r="J89" s="3">
+        <v>694500</v>
+      </c>
+      <c r="K89" s="3">
         <v>768200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>431200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>71500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>612600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>154900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>108400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>72800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>110500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4396,58 +4615,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11557000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10854000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9755000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6144000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7154000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5586000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5481100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4134500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5122700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-139200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-249400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-203500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-237800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-165400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-136600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100700</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4496,8 +4719,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4546,58 +4772,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-554100</v>
+        <v>-634500</v>
       </c>
       <c r="E94" s="3">
-        <v>-525900</v>
+        <v>-564800</v>
       </c>
       <c r="F94" s="3">
-        <v>-401700</v>
+        <v>-536000</v>
       </c>
       <c r="G94" s="3">
-        <v>-466900</v>
+        <v>-409500</v>
       </c>
       <c r="H94" s="3">
-        <v>-310800</v>
+        <v>-476000</v>
       </c>
       <c r="I94" s="3">
-        <v>-270900</v>
+        <v>-316800</v>
       </c>
       <c r="J94" s="3">
+        <v>-276100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-259700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-269800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-292800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-201100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-243000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1627900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-223500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-316200</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4616,8 +4848,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4666,8 +4899,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4716,8 +4952,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4766,8 +5005,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4816,154 +5058,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1200</v>
+        <v>707400</v>
       </c>
       <c r="E100" s="3">
-        <v>-182800</v>
+        <v>-1300</v>
       </c>
       <c r="F100" s="3">
-        <v>-3900</v>
+        <v>-186300</v>
       </c>
       <c r="G100" s="3">
-        <v>-362800</v>
+        <v>-4000</v>
       </c>
       <c r="H100" s="3">
-        <v>-82700</v>
+        <v>-369800</v>
       </c>
       <c r="I100" s="3">
-        <v>44000</v>
+        <v>-84300</v>
       </c>
       <c r="J100" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-163800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-188000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>111900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-292100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-145300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1931800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>118600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>192600</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>82300</v>
+        <v>-5000</v>
       </c>
       <c r="E101" s="3">
-        <v>50600</v>
+        <v>83900</v>
       </c>
       <c r="F101" s="3">
+        <v>51600</v>
+      </c>
+      <c r="G101" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H101" s="3">
+        <v>42200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+      <c r="O101" s="3">
         <v>8800</v>
       </c>
-      <c r="G101" s="3">
-        <v>41400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-16700</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>8800</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-209100</v>
+        <v>185100</v>
       </c>
       <c r="E102" s="3">
-        <v>-62600</v>
+        <v>-213200</v>
       </c>
       <c r="F102" s="3">
-        <v>-162500</v>
+        <v>-63800</v>
       </c>
       <c r="G102" s="3">
-        <v>224000</v>
+        <v>-165700</v>
       </c>
       <c r="H102" s="3">
-        <v>312700</v>
+        <v>228300</v>
       </c>
       <c r="I102" s="3">
-        <v>437800</v>
+        <v>318700</v>
       </c>
       <c r="J102" s="3">
+        <v>446200</v>
+      </c>
+      <c r="K102" s="3">
         <v>342800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>185900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-293400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>369900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -656,253 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2890600</v>
+        <v>3110700</v>
       </c>
       <c r="E8" s="3">
-        <v>3296100</v>
+        <v>2993100</v>
       </c>
       <c r="F8" s="3">
-        <v>3695600</v>
+        <v>3413000</v>
       </c>
       <c r="G8" s="3">
-        <v>3830000</v>
+        <v>3826700</v>
       </c>
       <c r="H8" s="3">
-        <v>4475600</v>
+        <v>3965900</v>
       </c>
       <c r="I8" s="3">
-        <v>4895200</v>
+        <v>4634300</v>
       </c>
       <c r="J8" s="3">
+        <v>5068900</v>
+      </c>
+      <c r="K8" s="3">
         <v>3938600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2937400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2617200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1267800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1661200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1587400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1755800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1279600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>945000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>840400</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2751300</v>
+        <v>2954800</v>
       </c>
       <c r="E9" s="3">
-        <v>2735200</v>
+        <v>2848900</v>
       </c>
       <c r="F9" s="3">
-        <v>2842800</v>
+        <v>2832200</v>
       </c>
       <c r="G9" s="3">
-        <v>2787300</v>
+        <v>2943700</v>
       </c>
       <c r="H9" s="3">
-        <v>3179600</v>
+        <v>2886200</v>
       </c>
       <c r="I9" s="3">
-        <v>2916500</v>
+        <v>3292400</v>
       </c>
       <c r="J9" s="3">
+        <v>3020000</v>
+      </c>
+      <c r="K9" s="3">
         <v>2369400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2220700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2121800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1276900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1583900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1516400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1573800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1242100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>788400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>658500</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>139300</v>
+        <v>156000</v>
       </c>
       <c r="E10" s="3">
-        <v>560900</v>
+        <v>144200</v>
       </c>
       <c r="F10" s="3">
-        <v>852800</v>
+        <v>580800</v>
       </c>
       <c r="G10" s="3">
-        <v>1042700</v>
+        <v>883000</v>
       </c>
       <c r="H10" s="3">
-        <v>1296000</v>
+        <v>1079700</v>
       </c>
       <c r="I10" s="3">
-        <v>1978700</v>
+        <v>1341900</v>
       </c>
       <c r="J10" s="3">
+        <v>2048900</v>
+      </c>
+      <c r="K10" s="3">
         <v>1569200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>716700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>495400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-9100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>182100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>37500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>156700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>181900</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +934,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,11 +985,14 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1028,61 +1044,67 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2592000</v>
+        <v>466000</v>
       </c>
       <c r="E14" s="3">
-        <v>-4600</v>
+        <v>2684000</v>
       </c>
       <c r="F14" s="3">
-        <v>19900</v>
+        <v>-4800</v>
       </c>
       <c r="G14" s="3">
-        <v>7800</v>
+        <v>20600</v>
       </c>
       <c r="H14" s="3">
-        <v>289600</v>
+        <v>8100</v>
       </c>
       <c r="I14" s="3">
-        <v>2100</v>
+        <v>299800</v>
       </c>
       <c r="J14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K14" s="3">
         <v>89500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>51000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>201200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>154400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>222800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-81400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1134,8 +1156,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1152,114 +1177,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5347100</v>
+        <v>3428400</v>
       </c>
       <c r="E17" s="3">
-        <v>2732900</v>
+        <v>5536800</v>
       </c>
       <c r="F17" s="3">
-        <v>2868500</v>
+        <v>2829800</v>
       </c>
       <c r="G17" s="3">
-        <v>2801300</v>
+        <v>2970200</v>
       </c>
       <c r="H17" s="3">
-        <v>3473800</v>
+        <v>2900600</v>
       </c>
       <c r="I17" s="3">
-        <v>2936900</v>
+        <v>3597000</v>
       </c>
       <c r="J17" s="3">
+        <v>3041100</v>
+      </c>
+      <c r="K17" s="3">
         <v>2470600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2258600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2183400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1270700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1795300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1548400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1735800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1472600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>727500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2456600</v>
+        <v>-317700</v>
       </c>
       <c r="E18" s="3">
-        <v>563200</v>
+        <v>-2543700</v>
       </c>
       <c r="F18" s="3">
-        <v>827100</v>
+        <v>583200</v>
       </c>
       <c r="G18" s="3">
-        <v>1028800</v>
+        <v>856500</v>
       </c>
       <c r="H18" s="3">
-        <v>1001800</v>
+        <v>1065200</v>
       </c>
       <c r="I18" s="3">
-        <v>1958300</v>
+        <v>1037300</v>
       </c>
       <c r="J18" s="3">
+        <v>2027800</v>
+      </c>
+      <c r="K18" s="3">
         <v>1467900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>678900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>433800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-134100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>39000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-193000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>217600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>118500</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1279,273 +1311,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-242300</v>
+        <v>56200</v>
       </c>
       <c r="E20" s="3">
-        <v>54000</v>
+        <v>-250900</v>
       </c>
       <c r="F20" s="3">
-        <v>-251400</v>
+        <v>55900</v>
       </c>
       <c r="G20" s="3">
-        <v>-15600</v>
+        <v>-260300</v>
       </c>
       <c r="H20" s="3">
-        <v>-255700</v>
+        <v>-16200</v>
       </c>
       <c r="I20" s="3">
-        <v>-54700</v>
+        <v>-264800</v>
       </c>
       <c r="J20" s="3">
+        <v>-56600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-138400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-328300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-74600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>104800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-85200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-76400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2668900</v>
+        <v>-28500</v>
       </c>
       <c r="E21" s="3">
-        <v>874600</v>
+        <v>-2763600</v>
       </c>
       <c r="F21" s="3">
-        <v>610500</v>
+        <v>905700</v>
       </c>
       <c r="G21" s="3">
-        <v>1188600</v>
+        <v>632200</v>
       </c>
       <c r="H21" s="3">
-        <v>784000</v>
+        <v>1230700</v>
       </c>
       <c r="I21" s="3">
-        <v>2110300</v>
+        <v>811800</v>
       </c>
       <c r="J21" s="3">
+        <v>2185100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1367900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>865400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>177800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>281500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-103100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>217300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>45900</v>
+        <v>74600</v>
       </c>
       <c r="E22" s="3">
-        <v>40900</v>
+        <v>47500</v>
       </c>
       <c r="F22" s="3">
-        <v>35100</v>
+        <v>42300</v>
       </c>
       <c r="G22" s="3">
-        <v>35300</v>
+        <v>36300</v>
       </c>
       <c r="H22" s="3">
-        <v>29100</v>
+        <v>36500</v>
       </c>
       <c r="I22" s="3">
-        <v>32500</v>
+        <v>30100</v>
       </c>
       <c r="J22" s="3">
+        <v>33600</v>
+      </c>
+      <c r="K22" s="3">
         <v>39900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>52500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>77100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>78000</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2744700</v>
+        <v>-336000</v>
       </c>
       <c r="E23" s="3">
-        <v>576300</v>
+        <v>-2842100</v>
       </c>
       <c r="F23" s="3">
-        <v>540700</v>
+        <v>596700</v>
       </c>
       <c r="G23" s="3">
-        <v>977900</v>
+        <v>559800</v>
       </c>
       <c r="H23" s="3">
-        <v>716900</v>
+        <v>1012600</v>
       </c>
       <c r="I23" s="3">
-        <v>1871100</v>
+        <v>742400</v>
       </c>
       <c r="J23" s="3">
+        <v>1937500</v>
+      </c>
+      <c r="K23" s="3">
         <v>1289600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>629000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>53600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-124600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-99400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-347400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>208700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-284100</v>
+        <v>66200</v>
       </c>
       <c r="E24" s="3">
-        <v>152600</v>
+        <v>-294100</v>
       </c>
       <c r="F24" s="3">
-        <v>179400</v>
+        <v>158000</v>
       </c>
       <c r="G24" s="3">
-        <v>306300</v>
+        <v>185700</v>
       </c>
       <c r="H24" s="3">
-        <v>255600</v>
+        <v>317100</v>
       </c>
       <c r="I24" s="3">
-        <v>493300</v>
+        <v>264700</v>
       </c>
       <c r="J24" s="3">
+        <v>510800</v>
+      </c>
+      <c r="K24" s="3">
         <v>152800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>109500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-115400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>62100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-166600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-27600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>39800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1597,114 +1645,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2460700</v>
+        <v>-402200</v>
       </c>
       <c r="E26" s="3">
-        <v>423700</v>
+        <v>-2547900</v>
       </c>
       <c r="F26" s="3">
-        <v>361300</v>
+        <v>438700</v>
       </c>
       <c r="G26" s="3">
-        <v>671600</v>
+        <v>374100</v>
       </c>
       <c r="H26" s="3">
-        <v>461300</v>
+        <v>695400</v>
       </c>
       <c r="I26" s="3">
-        <v>1377900</v>
+        <v>477700</v>
       </c>
       <c r="J26" s="3">
+        <v>1426700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1136900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>519500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-161400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-319800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>168900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2459500</v>
+        <v>-421000</v>
       </c>
       <c r="E27" s="3">
-        <v>404000</v>
+        <v>-2546700</v>
       </c>
       <c r="F27" s="3">
-        <v>347200</v>
+        <v>418300</v>
       </c>
       <c r="G27" s="3">
-        <v>653900</v>
+        <v>359500</v>
       </c>
       <c r="H27" s="3">
-        <v>447200</v>
+        <v>677100</v>
       </c>
       <c r="I27" s="3">
-        <v>1351600</v>
+        <v>463100</v>
       </c>
       <c r="J27" s="3">
+        <v>1399500</v>
+      </c>
+      <c r="K27" s="3">
         <v>1084400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>501100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-160000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-319800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>179500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1756,8 +1813,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1809,8 +1869,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1862,8 +1925,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1915,114 +1981,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>242300</v>
+        <v>-56200</v>
       </c>
       <c r="E32" s="3">
-        <v>-54000</v>
+        <v>250900</v>
       </c>
       <c r="F32" s="3">
-        <v>251400</v>
+        <v>-55900</v>
       </c>
       <c r="G32" s="3">
-        <v>15600</v>
+        <v>260300</v>
       </c>
       <c r="H32" s="3">
-        <v>255700</v>
+        <v>16200</v>
       </c>
       <c r="I32" s="3">
-        <v>54700</v>
+        <v>264800</v>
       </c>
       <c r="J32" s="3">
+        <v>56600</v>
+      </c>
+      <c r="K32" s="3">
         <v>138400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>328300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>74600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-104800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>85200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>76400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2459500</v>
+        <v>-421000</v>
       </c>
       <c r="E33" s="3">
-        <v>404000</v>
+        <v>-2546700</v>
       </c>
       <c r="F33" s="3">
-        <v>347200</v>
+        <v>418300</v>
       </c>
       <c r="G33" s="3">
-        <v>653900</v>
+        <v>359500</v>
       </c>
       <c r="H33" s="3">
-        <v>447200</v>
+        <v>677100</v>
       </c>
       <c r="I33" s="3">
-        <v>1351600</v>
+        <v>463100</v>
       </c>
       <c r="J33" s="3">
+        <v>1399500</v>
+      </c>
+      <c r="K33" s="3">
         <v>1084400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>501100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-160000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-319800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>179500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2074,119 +2149,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2459500</v>
+        <v>-421000</v>
       </c>
       <c r="E35" s="3">
-        <v>404000</v>
+        <v>-2546700</v>
       </c>
       <c r="F35" s="3">
-        <v>347200</v>
+        <v>418300</v>
       </c>
       <c r="G35" s="3">
-        <v>653900</v>
+        <v>359500</v>
       </c>
       <c r="H35" s="3">
-        <v>447200</v>
+        <v>677100</v>
       </c>
       <c r="I35" s="3">
-        <v>1351600</v>
+        <v>463100</v>
       </c>
       <c r="J35" s="3">
+        <v>1399500</v>
+      </c>
+      <c r="K35" s="3">
         <v>1084400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>501100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-160000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-319800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>179500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2206,8 +2290,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2227,61 +2312,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1391000</v>
+        <v>876800</v>
       </c>
       <c r="E41" s="3">
-        <v>1205900</v>
+        <v>1440300</v>
       </c>
       <c r="F41" s="3">
-        <v>1419100</v>
+        <v>1248700</v>
       </c>
       <c r="G41" s="3">
-        <v>1482800</v>
+        <v>1469400</v>
       </c>
       <c r="H41" s="3">
-        <v>1648500</v>
+        <v>1535400</v>
       </c>
       <c r="I41" s="3">
-        <v>1420200</v>
+        <v>1707000</v>
       </c>
       <c r="J41" s="3">
+        <v>1470600</v>
+      </c>
+      <c r="K41" s="3">
         <v>1101400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>642800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>297800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>321300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>158300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>139400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>135700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>434300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>55300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2333,134 +2422,143 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>538700</v>
+        <v>569300</v>
       </c>
       <c r="E43" s="3">
-        <v>478000</v>
+        <v>557800</v>
       </c>
       <c r="F43" s="3">
-        <v>451900</v>
+        <v>494900</v>
       </c>
       <c r="G43" s="3">
-        <v>485900</v>
+        <v>467900</v>
       </c>
       <c r="H43" s="3">
-        <v>499500</v>
+        <v>503100</v>
       </c>
       <c r="I43" s="3">
-        <v>450900</v>
+        <v>517200</v>
       </c>
       <c r="J43" s="3">
+        <v>466900</v>
+      </c>
+      <c r="K43" s="3">
         <v>383700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>258000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>267100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>295100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>456600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>434600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>422000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>389000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>346200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1434700</v>
+        <v>1457500</v>
       </c>
       <c r="E44" s="3">
-        <v>1399100</v>
+        <v>1485600</v>
       </c>
       <c r="F44" s="3">
-        <v>1435800</v>
+        <v>1448800</v>
       </c>
       <c r="G44" s="3">
-        <v>1469600</v>
+        <v>1486700</v>
       </c>
       <c r="H44" s="3">
-        <v>1364900</v>
+        <v>1521700</v>
       </c>
       <c r="I44" s="3">
-        <v>1602000</v>
+        <v>1413300</v>
       </c>
       <c r="J44" s="3">
+        <v>1658800</v>
+      </c>
+      <c r="K44" s="3">
         <v>1357900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>898200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>821500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>765500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>328900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>281200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>232000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>197200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>38700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I45" s="3" t="s">
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="I45" s="3">
+        <v>15800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -2471,241 +2569,256 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>6500</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>84300</v>
       </c>
-      <c r="P45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3364400</v>
+        <v>2903700</v>
       </c>
       <c r="E46" s="3">
-        <v>3083000</v>
+        <v>3483700</v>
       </c>
       <c r="F46" s="3">
-        <v>3306800</v>
+        <v>3192300</v>
       </c>
       <c r="G46" s="3">
-        <v>3438400</v>
+        <v>3424100</v>
       </c>
       <c r="H46" s="3">
-        <v>3528100</v>
+        <v>3560300</v>
       </c>
       <c r="I46" s="3">
-        <v>3473100</v>
+        <v>3653200</v>
       </c>
       <c r="J46" s="3">
+        <v>3596300</v>
+      </c>
+      <c r="K46" s="3">
         <v>2843000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1799000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1386400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1388400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>943800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>939500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>789700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1020500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>440200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>203200</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>417500</v>
+        <v>639500</v>
       </c>
       <c r="E47" s="3">
-        <v>547400</v>
+        <v>611400</v>
       </c>
       <c r="F47" s="3">
-        <v>504400</v>
+        <v>756300</v>
       </c>
       <c r="G47" s="3">
-        <v>480200</v>
+        <v>710500</v>
       </c>
       <c r="H47" s="3">
-        <v>448700</v>
+        <v>654300</v>
       </c>
       <c r="I47" s="3">
-        <v>402100</v>
+        <v>654300</v>
       </c>
       <c r="J47" s="3">
+        <v>472200</v>
+      </c>
+      <c r="K47" s="3">
         <v>350600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>326200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>250200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>242700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>251400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>197500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>166300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>174400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>143600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3368500</v>
+        <v>3486000</v>
       </c>
       <c r="E48" s="3">
-        <v>5084700</v>
+        <v>3488000</v>
       </c>
       <c r="F48" s="3">
-        <v>4200600</v>
+        <v>5265000</v>
       </c>
       <c r="G48" s="3">
-        <v>3780700</v>
+        <v>4349500</v>
       </c>
       <c r="H48" s="3">
-        <v>3413000</v>
+        <v>3914700</v>
       </c>
       <c r="I48" s="3">
-        <v>3349400</v>
+        <v>3534000</v>
       </c>
       <c r="J48" s="3">
+        <v>3468200</v>
+      </c>
+      <c r="K48" s="3">
         <v>3313900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3535500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3065000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3057100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3388600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3532300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3384000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3620500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1556800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1326500</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>27300</v>
+        <v>111200</v>
       </c>
       <c r="E49" s="3">
-        <v>498000</v>
+        <v>28300</v>
       </c>
       <c r="F49" s="3">
-        <v>452900</v>
+        <v>515700</v>
       </c>
       <c r="G49" s="3">
-        <v>434700</v>
+        <v>468900</v>
       </c>
       <c r="H49" s="3">
-        <v>420500</v>
+        <v>450100</v>
       </c>
       <c r="I49" s="3">
-        <v>379600</v>
+        <v>435400</v>
       </c>
       <c r="J49" s="3">
+        <v>393100</v>
+      </c>
+      <c r="K49" s="3">
         <v>389900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>446400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>363200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>371400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>427900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>465500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>420700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>453400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>53500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2757,8 +2870,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2810,61 +2926,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>601200</v>
+        <v>462000</v>
       </c>
       <c r="E52" s="3">
-        <v>605600</v>
+        <v>443400</v>
       </c>
       <c r="F52" s="3">
-        <v>603400</v>
+        <v>437600</v>
       </c>
       <c r="G52" s="3">
-        <v>496500</v>
+        <v>436600</v>
       </c>
       <c r="H52" s="3">
-        <v>515600</v>
+        <v>357000</v>
       </c>
       <c r="I52" s="3">
-        <v>365900</v>
+        <v>344200</v>
       </c>
       <c r="J52" s="3">
+        <v>323100</v>
+      </c>
+      <c r="K52" s="3">
         <v>400400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>311400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>290900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>273300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>262800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>248400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>243300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>227000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>190200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>159700</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2916,61 +3038,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>7778800</v>
+        <v>7602300</v>
       </c>
       <c r="E54" s="3">
-        <v>9818700</v>
+        <v>8054700</v>
       </c>
       <c r="F54" s="3">
-        <v>9068100</v>
+        <v>10166900</v>
       </c>
       <c r="G54" s="3">
-        <v>8630400</v>
+        <v>9389700</v>
       </c>
       <c r="H54" s="3">
-        <v>8325900</v>
+        <v>8936500</v>
       </c>
       <c r="I54" s="3">
-        <v>7970200</v>
+        <v>8621200</v>
       </c>
       <c r="J54" s="3">
+        <v>8252900</v>
+      </c>
+      <c r="K54" s="3">
         <v>7297900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6418700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5355800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5332800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5274600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5383200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5004000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5495800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2384400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1876100</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2990,8 +3118,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3011,326 +3140,345 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>896000</v>
+        <v>867700</v>
       </c>
       <c r="E57" s="3">
-        <v>836800</v>
+        <v>927700</v>
       </c>
       <c r="F57" s="3">
-        <v>851800</v>
+        <v>866500</v>
       </c>
       <c r="G57" s="3">
-        <v>783200</v>
+        <v>882000</v>
       </c>
       <c r="H57" s="3">
-        <v>825100</v>
+        <v>811000</v>
       </c>
       <c r="I57" s="3">
-        <v>807800</v>
+        <v>854400</v>
       </c>
       <c r="J57" s="3">
+        <v>836500</v>
+      </c>
+      <c r="K57" s="3">
         <v>718700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>631000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>607600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>598600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>488000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>453700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>440100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>476300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>296100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>221800</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>853300</v>
+        <v>275700</v>
       </c>
       <c r="E58" s="3">
-        <v>18200</v>
+        <v>883600</v>
       </c>
       <c r="F58" s="3">
-        <v>12700</v>
+        <v>18900</v>
       </c>
       <c r="G58" s="3">
-        <v>12700</v>
+        <v>13100</v>
       </c>
       <c r="H58" s="3">
-        <v>11500</v>
+        <v>13200</v>
       </c>
       <c r="I58" s="3">
-        <v>362100</v>
+        <v>11900</v>
       </c>
       <c r="J58" s="3">
+        <v>375000</v>
+      </c>
+      <c r="K58" s="3">
         <v>53800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>73400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>298800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>384300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>109000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>504100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>43000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>232000</v>
+        <v>248300</v>
       </c>
       <c r="E59" s="3">
-        <v>125700</v>
+        <v>240200</v>
       </c>
       <c r="F59" s="3">
-        <v>235800</v>
+        <v>130200</v>
       </c>
       <c r="G59" s="3">
-        <v>226900</v>
+        <v>244200</v>
       </c>
       <c r="H59" s="3">
-        <v>281200</v>
+        <v>234900</v>
       </c>
       <c r="I59" s="3">
-        <v>100700</v>
+        <v>291200</v>
       </c>
       <c r="J59" s="3">
+        <v>104200</v>
+      </c>
+      <c r="K59" s="3">
         <v>179100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>211600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>143700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>199200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>36500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1981300</v>
+        <v>1391800</v>
       </c>
       <c r="E60" s="3">
-        <v>980800</v>
+        <v>2051500</v>
       </c>
       <c r="F60" s="3">
-        <v>1100300</v>
+        <v>1015500</v>
       </c>
       <c r="G60" s="3">
-        <v>1022800</v>
+        <v>1139300</v>
       </c>
       <c r="H60" s="3">
-        <v>1117800</v>
+        <v>1059100</v>
       </c>
       <c r="I60" s="3">
-        <v>1270600</v>
+        <v>1157500</v>
       </c>
       <c r="J60" s="3">
+        <v>1315700</v>
+      </c>
+      <c r="K60" s="3">
         <v>951600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>916000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>759200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1096600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>908800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>507900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>555000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>989700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>357600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>466900</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1378500</v>
+        <v>1853200</v>
       </c>
       <c r="E61" s="3">
-        <v>1394100</v>
+        <v>1427300</v>
       </c>
       <c r="F61" s="3">
-        <v>1241500</v>
+        <v>1443500</v>
       </c>
       <c r="G61" s="3">
-        <v>1143500</v>
+        <v>1285600</v>
       </c>
       <c r="H61" s="3">
-        <v>1108400</v>
+        <v>1184000</v>
       </c>
       <c r="I61" s="3">
-        <v>588900</v>
+        <v>1147700</v>
       </c>
       <c r="J61" s="3">
+        <v>609800</v>
+      </c>
+      <c r="K61" s="3">
         <v>964300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1352400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1270200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1181600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1137600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1882700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1578200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1507200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>469900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1610700</v>
+        <v>1734700</v>
       </c>
       <c r="E62" s="3">
-        <v>1992900</v>
+        <v>1667800</v>
       </c>
       <c r="F62" s="3">
-        <v>1773800</v>
+        <v>2063600</v>
       </c>
       <c r="G62" s="3">
-        <v>1601300</v>
+        <v>1836700</v>
       </c>
       <c r="H62" s="3">
-        <v>1672900</v>
+        <v>1658000</v>
       </c>
       <c r="I62" s="3">
-        <v>1575400</v>
+        <v>1732200</v>
       </c>
       <c r="J62" s="3">
+        <v>1631300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1533500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1693100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1676400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1424800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1692500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1298800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1292200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1396700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>615700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3382,8 +3530,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3435,8 +3586,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3488,61 +3642,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5127000</v>
+        <v>5156500</v>
       </c>
       <c r="E66" s="3">
-        <v>4540500</v>
+        <v>5308800</v>
       </c>
       <c r="F66" s="3">
-        <v>4273600</v>
+        <v>4701500</v>
       </c>
       <c r="G66" s="3">
-        <v>3924500</v>
+        <v>4425200</v>
       </c>
       <c r="H66" s="3">
-        <v>4005400</v>
+        <v>4063700</v>
       </c>
       <c r="I66" s="3">
-        <v>3507000</v>
+        <v>4147400</v>
       </c>
       <c r="J66" s="3">
+        <v>3631400</v>
+      </c>
+      <c r="K66" s="3">
         <v>3571200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4035800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3783500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3770300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3797100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3690800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3426700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3894700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1444200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1047600</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3562,8 +3722,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3615,8 +3776,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3668,8 +3832,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3721,8 +3888,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3774,61 +3944,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1473900</v>
+        <v>1226000</v>
       </c>
       <c r="E72" s="3">
-        <v>4100200</v>
+        <v>1526100</v>
       </c>
       <c r="F72" s="3">
-        <v>3616400</v>
+        <v>4245600</v>
       </c>
       <c r="G72" s="3">
-        <v>2276200</v>
+        <v>3744700</v>
       </c>
       <c r="H72" s="3">
-        <v>3142500</v>
+        <v>2356900</v>
       </c>
       <c r="I72" s="3">
-        <v>1621400</v>
+        <v>3254000</v>
       </c>
       <c r="J72" s="3">
+        <v>1678900</v>
+      </c>
+      <c r="K72" s="3">
         <v>2085900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>212000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-582400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-628000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-675700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-609100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-703100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-709000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-301900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-413700</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3880,8 +4056,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3933,8 +4112,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3986,61 +4168,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2651900</v>
+        <v>2445800</v>
       </c>
       <c r="E76" s="3">
-        <v>5278200</v>
+        <v>2745900</v>
       </c>
       <c r="F76" s="3">
-        <v>4794500</v>
+        <v>5465400</v>
       </c>
       <c r="G76" s="3">
-        <v>4705900</v>
+        <v>4964500</v>
       </c>
       <c r="H76" s="3">
-        <v>4320600</v>
+        <v>4872800</v>
       </c>
       <c r="I76" s="3">
-        <v>4463200</v>
+        <v>4473800</v>
       </c>
       <c r="J76" s="3">
+        <v>4621500</v>
+      </c>
+      <c r="K76" s="3">
         <v>3726700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2382900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1572200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1562500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1477500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1692400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1577300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1601100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>940200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4092,119 +4280,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2459500</v>
+        <v>-421000</v>
       </c>
       <c r="E81" s="3">
-        <v>404000</v>
+        <v>-2546700</v>
       </c>
       <c r="F81" s="3">
-        <v>347200</v>
+        <v>418300</v>
       </c>
       <c r="G81" s="3">
-        <v>653900</v>
+        <v>359500</v>
       </c>
       <c r="H81" s="3">
-        <v>447200</v>
+        <v>677100</v>
       </c>
       <c r="I81" s="3">
-        <v>1351600</v>
+        <v>463100</v>
       </c>
       <c r="J81" s="3">
+        <v>1399500</v>
+      </c>
+      <c r="K81" s="3">
         <v>1084400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>501100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-160000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-319800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>179500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4224,8 +4421,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4277,8 +4475,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4330,8 +4531,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4383,8 +4587,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4436,8 +4643,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4489,8 +4699,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4542,61 +4755,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>117100</v>
+        <v>217300</v>
       </c>
       <c r="E89" s="3">
-        <v>269000</v>
+        <v>121300</v>
       </c>
       <c r="F89" s="3">
-        <v>607000</v>
+        <v>278500</v>
       </c>
       <c r="G89" s="3">
-        <v>238800</v>
+        <v>628500</v>
       </c>
       <c r="H89" s="3">
-        <v>1031800</v>
+        <v>247300</v>
       </c>
       <c r="I89" s="3">
-        <v>723600</v>
+        <v>1068400</v>
       </c>
       <c r="J89" s="3">
+        <v>749200</v>
+      </c>
+      <c r="K89" s="3">
         <v>694500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>768200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>431200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>71500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>612600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>154900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>108400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>110500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4616,61 +4835,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11147000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11557000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10854000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9755000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6144000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7154000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5586000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5481100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4134500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5122700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-139200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-249400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-203500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-237800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-165400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-136600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100700</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4722,8 +4945,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4775,61 +5001,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-634500</v>
+        <v>-798700</v>
       </c>
       <c r="E94" s="3">
-        <v>-564800</v>
+        <v>-657000</v>
       </c>
       <c r="F94" s="3">
-        <v>-536000</v>
+        <v>-584900</v>
       </c>
       <c r="G94" s="3">
-        <v>-409500</v>
+        <v>-555000</v>
       </c>
       <c r="H94" s="3">
-        <v>-476000</v>
+        <v>-424000</v>
       </c>
       <c r="I94" s="3">
-        <v>-316800</v>
+        <v>-492800</v>
       </c>
       <c r="J94" s="3">
+        <v>-328100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-276100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-259700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-269800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-292800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-201100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-243000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1627900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-223500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-316200</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4849,8 +5081,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4902,8 +5135,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4955,8 +5191,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5008,8 +5247,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5061,163 +5303,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>707400</v>
+        <v>23400</v>
       </c>
       <c r="E100" s="3">
+        <v>732500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1300</v>
       </c>
-      <c r="F100" s="3">
-        <v>-186300</v>
-      </c>
       <c r="G100" s="3">
-        <v>-4000</v>
+        <v>-192900</v>
       </c>
       <c r="H100" s="3">
-        <v>-369800</v>
+        <v>-4100</v>
       </c>
       <c r="I100" s="3">
-        <v>-84300</v>
+        <v>-382900</v>
       </c>
       <c r="J100" s="3">
+        <v>-87300</v>
+      </c>
+      <c r="K100" s="3">
         <v>44800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-163800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-188000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>111900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-292100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-145300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1931800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>118600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>192600</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5000</v>
+        <v>-5500</v>
       </c>
       <c r="E101" s="3">
-        <v>83900</v>
+        <v>-5100</v>
       </c>
       <c r="F101" s="3">
-        <v>51600</v>
+        <v>86900</v>
       </c>
       <c r="G101" s="3">
-        <v>8900</v>
+        <v>53400</v>
       </c>
       <c r="H101" s="3">
-        <v>42200</v>
+        <v>9200</v>
       </c>
       <c r="I101" s="3">
-        <v>-3700</v>
+        <v>43700</v>
       </c>
       <c r="J101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6900</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>185100</v>
+        <v>-563500</v>
       </c>
       <c r="E102" s="3">
-        <v>-213200</v>
+        <v>191600</v>
       </c>
       <c r="F102" s="3">
-        <v>-63800</v>
+        <v>-220700</v>
       </c>
       <c r="G102" s="3">
-        <v>-165700</v>
+        <v>-66000</v>
       </c>
       <c r="H102" s="3">
-        <v>228300</v>
+        <v>-171500</v>
       </c>
       <c r="I102" s="3">
-        <v>318700</v>
+        <v>236400</v>
       </c>
       <c r="J102" s="3">
+        <v>330000</v>
+      </c>
+      <c r="K102" s="3">
         <v>446200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>342800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>185900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-293400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>369900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -662,12 +662,12 @@
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -698,22 +698,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -751,25 +751,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3110700</v>
+        <v>1512000</v>
       </c>
       <c r="E8" s="3">
-        <v>2993100</v>
+        <v>1461000</v>
       </c>
       <c r="F8" s="3">
-        <v>3413000</v>
+        <v>1451900</v>
       </c>
       <c r="G8" s="3">
-        <v>3826700</v>
+        <v>1407600</v>
       </c>
       <c r="H8" s="3">
-        <v>3965900</v>
+        <v>1607800</v>
       </c>
       <c r="I8" s="3">
-        <v>4634300</v>
+        <v>1709500</v>
       </c>
       <c r="J8" s="3">
-        <v>5068900</v>
+        <v>1997200</v>
       </c>
       <c r="K8" s="3">
         <v>3938600</v>
@@ -807,25 +807,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2954800</v>
+        <v>1316400</v>
       </c>
       <c r="E9" s="3">
-        <v>2848900</v>
+        <v>1272000</v>
       </c>
       <c r="F9" s="3">
-        <v>2832200</v>
+        <v>1498800</v>
       </c>
       <c r="G9" s="3">
-        <v>2943700</v>
+        <v>1453100</v>
       </c>
       <c r="H9" s="3">
-        <v>2886200</v>
+        <v>1192900</v>
       </c>
       <c r="I9" s="3">
-        <v>3292400</v>
+        <v>1268300</v>
       </c>
       <c r="J9" s="3">
-        <v>3020000</v>
+        <v>1605700</v>
       </c>
       <c r="K9" s="3">
         <v>2369400</v>
@@ -863,25 +863,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>156000</v>
+        <v>195600</v>
       </c>
       <c r="E10" s="3">
-        <v>144200</v>
+        <v>189000</v>
       </c>
       <c r="F10" s="3">
-        <v>580800</v>
+        <v>-46900</v>
       </c>
       <c r="G10" s="3">
-        <v>883000</v>
+        <v>-45400</v>
       </c>
       <c r="H10" s="3">
-        <v>1079700</v>
+        <v>414900</v>
       </c>
       <c r="I10" s="3">
-        <v>1341900</v>
+        <v>441100</v>
       </c>
       <c r="J10" s="3">
-        <v>2048900</v>
+        <v>391400</v>
       </c>
       <c r="K10" s="3">
         <v>1569200</v>
@@ -1053,25 +1053,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>466000</v>
+        <v>203500</v>
       </c>
       <c r="E14" s="3">
-        <v>2684000</v>
+        <v>196600</v>
       </c>
       <c r="F14" s="3">
-        <v>-4800</v>
+        <v>231900</v>
       </c>
       <c r="G14" s="3">
-        <v>20600</v>
+        <v>224800</v>
       </c>
       <c r="H14" s="3">
-        <v>8100</v>
+        <v>-3600</v>
       </c>
       <c r="I14" s="3">
-        <v>299800</v>
+        <v>-3800</v>
       </c>
       <c r="J14" s="3">
-        <v>2200</v>
+        <v>9400</v>
       </c>
       <c r="K14" s="3">
         <v>89500</v>
@@ -1109,25 +1109,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>113600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>109800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>922900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>894700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>125600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>133500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>-94800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1184,25 +1184,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3428400</v>
+        <v>1495700</v>
       </c>
       <c r="E17" s="3">
-        <v>5536800</v>
+        <v>1445300</v>
       </c>
       <c r="F17" s="3">
-        <v>2829800</v>
+        <v>2546600</v>
       </c>
       <c r="G17" s="3">
-        <v>2970200</v>
+        <v>2468900</v>
       </c>
       <c r="H17" s="3">
-        <v>2900600</v>
+        <v>1375800</v>
       </c>
       <c r="I17" s="3">
-        <v>3597000</v>
+        <v>1462800</v>
       </c>
       <c r="J17" s="3">
-        <v>3041100</v>
+        <v>1580200</v>
       </c>
       <c r="K17" s="3">
         <v>2470600</v>
@@ -1240,25 +1240,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-317700</v>
+        <v>16300</v>
       </c>
       <c r="E18" s="3">
-        <v>-2543700</v>
+        <v>15700</v>
       </c>
       <c r="F18" s="3">
-        <v>583200</v>
+        <v>-1094700</v>
       </c>
       <c r="G18" s="3">
-        <v>856500</v>
+        <v>-1061300</v>
       </c>
       <c r="H18" s="3">
-        <v>1065200</v>
+        <v>232000</v>
       </c>
       <c r="I18" s="3">
-        <v>1037300</v>
+        <v>246700</v>
       </c>
       <c r="J18" s="3">
-        <v>2027800</v>
+        <v>416900</v>
       </c>
       <c r="K18" s="3">
         <v>1467900</v>
@@ -1318,25 +1318,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>56200</v>
+        <v>-51600</v>
       </c>
       <c r="E20" s="3">
-        <v>-250900</v>
+        <v>-49800</v>
       </c>
       <c r="F20" s="3">
-        <v>55900</v>
+        <v>37300</v>
       </c>
       <c r="G20" s="3">
-        <v>-260300</v>
+        <v>36200</v>
       </c>
       <c r="H20" s="3">
-        <v>-16200</v>
+        <v>-60400</v>
       </c>
       <c r="I20" s="3">
-        <v>-264800</v>
+        <v>-64200</v>
       </c>
       <c r="J20" s="3">
-        <v>-56600</v>
+        <v>103300</v>
       </c>
       <c r="K20" s="3">
         <v>-138400</v>
@@ -1374,25 +1374,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-28500</v>
+        <v>181400</v>
       </c>
       <c r="E21" s="3">
-        <v>-2763600</v>
+        <v>175300</v>
       </c>
       <c r="F21" s="3">
-        <v>905700</v>
+        <v>-209100</v>
       </c>
       <c r="G21" s="3">
-        <v>632200</v>
+        <v>-202700</v>
       </c>
       <c r="H21" s="3">
-        <v>1230700</v>
+        <v>418000</v>
       </c>
       <c r="I21" s="3">
-        <v>811800</v>
+        <v>444400</v>
       </c>
       <c r="J21" s="3">
-        <v>2185100</v>
+        <v>218800</v>
       </c>
       <c r="K21" s="3">
         <v>1367900</v>
@@ -1430,25 +1430,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>74600</v>
+        <v>48200</v>
       </c>
       <c r="E22" s="3">
-        <v>47500</v>
+        <v>46600</v>
       </c>
       <c r="F22" s="3">
-        <v>42300</v>
+        <v>32600</v>
       </c>
       <c r="G22" s="3">
-        <v>36300</v>
+        <v>31600</v>
       </c>
       <c r="H22" s="3">
-        <v>36500</v>
+        <v>33900</v>
       </c>
       <c r="I22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="J22" s="3">
         <v>30100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>33600</v>
       </c>
       <c r="K22" s="3">
         <v>39900</v>
@@ -1486,25 +1486,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-336000</v>
+        <v>-163300</v>
       </c>
       <c r="E23" s="3">
-        <v>-2842100</v>
+        <v>-157800</v>
       </c>
       <c r="F23" s="3">
-        <v>596700</v>
+        <v>-1378700</v>
       </c>
       <c r="G23" s="3">
-        <v>559800</v>
+        <v>-1336600</v>
       </c>
       <c r="H23" s="3">
-        <v>1012600</v>
+        <v>281100</v>
       </c>
       <c r="I23" s="3">
-        <v>742400</v>
+        <v>298900</v>
       </c>
       <c r="J23" s="3">
-        <v>1937500</v>
+        <v>292200</v>
       </c>
       <c r="K23" s="3">
         <v>1289600</v>
@@ -1542,25 +1542,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>66200</v>
+        <v>32200</v>
       </c>
       <c r="E24" s="3">
-        <v>-294100</v>
+        <v>31100</v>
       </c>
       <c r="F24" s="3">
-        <v>158000</v>
+        <v>-142700</v>
       </c>
       <c r="G24" s="3">
-        <v>185700</v>
+        <v>-138300</v>
       </c>
       <c r="H24" s="3">
-        <v>317100</v>
+        <v>74400</v>
       </c>
       <c r="I24" s="3">
-        <v>264700</v>
+        <v>79100</v>
       </c>
       <c r="J24" s="3">
-        <v>510800</v>
+        <v>96900</v>
       </c>
       <c r="K24" s="3">
         <v>152800</v>
@@ -1654,25 +1654,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-402200</v>
+        <v>-195500</v>
       </c>
       <c r="E26" s="3">
-        <v>-2547900</v>
+        <v>-188900</v>
       </c>
       <c r="F26" s="3">
-        <v>438700</v>
+        <v>-1236000</v>
       </c>
       <c r="G26" s="3">
-        <v>374100</v>
+        <v>-1198300</v>
       </c>
       <c r="H26" s="3">
-        <v>695400</v>
+        <v>206700</v>
       </c>
       <c r="I26" s="3">
-        <v>477700</v>
+        <v>219800</v>
       </c>
       <c r="J26" s="3">
-        <v>1426700</v>
+        <v>195300</v>
       </c>
       <c r="K26" s="3">
         <v>1136900</v>
@@ -1710,25 +1710,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-421000</v>
+        <v>-204700</v>
       </c>
       <c r="E27" s="3">
-        <v>-2546700</v>
+        <v>-197800</v>
       </c>
       <c r="F27" s="3">
-        <v>418300</v>
+        <v>-1235400</v>
       </c>
       <c r="G27" s="3">
-        <v>359500</v>
+        <v>-1197700</v>
       </c>
       <c r="H27" s="3">
-        <v>677100</v>
+        <v>197000</v>
       </c>
       <c r="I27" s="3">
-        <v>463100</v>
+        <v>209500</v>
       </c>
       <c r="J27" s="3">
-        <v>1399500</v>
+        <v>187600</v>
       </c>
       <c r="K27" s="3">
         <v>1084400</v>
@@ -1990,25 +1990,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-56200</v>
+        <v>51600</v>
       </c>
       <c r="E32" s="3">
-        <v>250900</v>
+        <v>49800</v>
       </c>
       <c r="F32" s="3">
-        <v>-55900</v>
+        <v>-37300</v>
       </c>
       <c r="G32" s="3">
-        <v>260300</v>
+        <v>-36200</v>
       </c>
       <c r="H32" s="3">
-        <v>16200</v>
+        <v>60400</v>
       </c>
       <c r="I32" s="3">
-        <v>264800</v>
+        <v>64200</v>
       </c>
       <c r="J32" s="3">
-        <v>56600</v>
+        <v>-103300</v>
       </c>
       <c r="K32" s="3">
         <v>138400</v>
@@ -2046,25 +2046,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-421000</v>
+        <v>-204700</v>
       </c>
       <c r="E33" s="3">
-        <v>-2546700</v>
+        <v>-197800</v>
       </c>
       <c r="F33" s="3">
-        <v>418300</v>
+        <v>-1235400</v>
       </c>
       <c r="G33" s="3">
-        <v>359500</v>
+        <v>-1197700</v>
       </c>
       <c r="H33" s="3">
-        <v>677100</v>
+        <v>197000</v>
       </c>
       <c r="I33" s="3">
-        <v>463100</v>
+        <v>209500</v>
       </c>
       <c r="J33" s="3">
-        <v>1399500</v>
+        <v>187600</v>
       </c>
       <c r="K33" s="3">
         <v>1084400</v>
@@ -2158,25 +2158,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-421000</v>
+        <v>-204700</v>
       </c>
       <c r="E35" s="3">
-        <v>-2546700</v>
+        <v>-197800</v>
       </c>
       <c r="F35" s="3">
-        <v>418300</v>
+        <v>-1235400</v>
       </c>
       <c r="G35" s="3">
-        <v>359500</v>
+        <v>-1197700</v>
       </c>
       <c r="H35" s="3">
-        <v>677100</v>
+        <v>197000</v>
       </c>
       <c r="I35" s="3">
-        <v>463100</v>
+        <v>209500</v>
       </c>
       <c r="J35" s="3">
-        <v>1399500</v>
+        <v>187600</v>
       </c>
       <c r="K35" s="3">
         <v>1084400</v>
@@ -2222,22 +2222,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2319,25 +2319,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>876800</v>
+        <v>852400</v>
       </c>
       <c r="E41" s="3">
-        <v>1440300</v>
+        <v>823600</v>
       </c>
       <c r="F41" s="3">
-        <v>1248700</v>
+        <v>1397400</v>
       </c>
       <c r="G41" s="3">
-        <v>1469400</v>
+        <v>1354700</v>
       </c>
       <c r="H41" s="3">
-        <v>1535400</v>
+        <v>1176400</v>
       </c>
       <c r="I41" s="3">
-        <v>1707000</v>
+        <v>1250800</v>
       </c>
       <c r="J41" s="3">
-        <v>1470600</v>
+        <v>1533800</v>
       </c>
       <c r="K41" s="3">
         <v>1101400</v>
@@ -2431,25 +2431,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>569300</v>
+        <v>553400</v>
       </c>
       <c r="E43" s="3">
-        <v>557800</v>
+        <v>534800</v>
       </c>
       <c r="F43" s="3">
-        <v>494900</v>
+        <v>474500</v>
       </c>
       <c r="G43" s="3">
-        <v>467900</v>
+        <v>460100</v>
       </c>
       <c r="H43" s="3">
-        <v>503100</v>
+        <v>466300</v>
       </c>
       <c r="I43" s="3">
-        <v>517200</v>
+        <v>495800</v>
       </c>
       <c r="J43" s="3">
-        <v>466900</v>
+        <v>463000</v>
       </c>
       <c r="K43" s="3">
         <v>383700</v>
@@ -2487,25 +2487,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1457500</v>
+        <v>1416900</v>
       </c>
       <c r="E44" s="3">
-        <v>1485600</v>
+        <v>1369200</v>
       </c>
       <c r="F44" s="3">
-        <v>1448800</v>
+        <v>1441300</v>
       </c>
       <c r="G44" s="3">
-        <v>1486700</v>
+        <v>1397300</v>
       </c>
       <c r="H44" s="3">
-        <v>1521700</v>
+        <v>1365000</v>
       </c>
       <c r="I44" s="3">
-        <v>1413300</v>
+        <v>1451300</v>
       </c>
       <c r="J44" s="3">
-        <v>1658800</v>
+        <v>1551900</v>
       </c>
       <c r="K44" s="3">
         <v>1357900</v>
@@ -2545,20 +2545,20 @@
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
-        <v>15800</v>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -2599,25 +2599,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2903700</v>
+        <v>2822700</v>
       </c>
       <c r="E46" s="3">
-        <v>3483700</v>
+        <v>2727600</v>
       </c>
       <c r="F46" s="3">
-        <v>3192300</v>
+        <v>3379800</v>
       </c>
       <c r="G46" s="3">
-        <v>3424100</v>
+        <v>3276700</v>
       </c>
       <c r="H46" s="3">
-        <v>3560300</v>
+        <v>3007700</v>
       </c>
       <c r="I46" s="3">
-        <v>3653200</v>
+        <v>3197900</v>
       </c>
       <c r="J46" s="3">
-        <v>3596300</v>
+        <v>3574100</v>
       </c>
       <c r="K46" s="3">
         <v>2843000</v>
@@ -2655,25 +2655,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>639500</v>
+        <v>585400</v>
       </c>
       <c r="E47" s="3">
-        <v>611400</v>
+        <v>565700</v>
       </c>
       <c r="F47" s="3">
-        <v>756300</v>
+        <v>564600</v>
       </c>
       <c r="G47" s="3">
-        <v>710500</v>
+        <v>547400</v>
       </c>
       <c r="H47" s="3">
-        <v>654300</v>
+        <v>670400</v>
       </c>
       <c r="I47" s="3">
-        <v>654300</v>
+        <v>712800</v>
       </c>
       <c r="J47" s="3">
-        <v>472200</v>
+        <v>694700</v>
       </c>
       <c r="K47" s="3">
         <v>350600</v>
@@ -2711,25 +2711,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3486000</v>
+        <v>3388900</v>
       </c>
       <c r="E48" s="3">
-        <v>3488000</v>
+        <v>3274600</v>
       </c>
       <c r="F48" s="3">
-        <v>5265000</v>
+        <v>3384000</v>
       </c>
       <c r="G48" s="3">
-        <v>4349500</v>
+        <v>3280800</v>
       </c>
       <c r="H48" s="3">
-        <v>3914700</v>
+        <v>4960500</v>
       </c>
       <c r="I48" s="3">
-        <v>3534000</v>
+        <v>5274200</v>
       </c>
       <c r="J48" s="3">
-        <v>3468200</v>
+        <v>4540200</v>
       </c>
       <c r="K48" s="3">
         <v>3313900</v>
@@ -2767,25 +2767,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>111200</v>
+        <v>108100</v>
       </c>
       <c r="E49" s="3">
-        <v>28300</v>
+        <v>104400</v>
       </c>
       <c r="F49" s="3">
-        <v>515700</v>
+        <v>27400</v>
       </c>
       <c r="G49" s="3">
-        <v>468900</v>
+        <v>26600</v>
       </c>
       <c r="H49" s="3">
-        <v>450100</v>
+        <v>485800</v>
       </c>
       <c r="I49" s="3">
-        <v>435400</v>
+        <v>516600</v>
       </c>
       <c r="J49" s="3">
-        <v>393100</v>
+        <v>489500</v>
       </c>
       <c r="K49" s="3">
         <v>389900</v>
@@ -2935,25 +2935,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>462000</v>
+        <v>377000</v>
       </c>
       <c r="E52" s="3">
-        <v>443400</v>
+        <v>364300</v>
       </c>
       <c r="F52" s="3">
-        <v>437600</v>
+        <v>352600</v>
       </c>
       <c r="G52" s="3">
-        <v>436600</v>
+        <v>341900</v>
       </c>
       <c r="H52" s="3">
-        <v>357000</v>
+        <v>337100</v>
       </c>
       <c r="I52" s="3">
-        <v>344200</v>
+        <v>358400</v>
       </c>
       <c r="J52" s="3">
-        <v>323100</v>
+        <v>359000</v>
       </c>
       <c r="K52" s="3">
         <v>400400</v>
@@ -3047,25 +3047,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>7602300</v>
+        <v>7390400</v>
       </c>
       <c r="E54" s="3">
-        <v>8054700</v>
+        <v>7141300</v>
       </c>
       <c r="F54" s="3">
-        <v>10166900</v>
+        <v>7814600</v>
       </c>
       <c r="G54" s="3">
-        <v>9389700</v>
+        <v>7576300</v>
       </c>
       <c r="H54" s="3">
-        <v>8936500</v>
+        <v>9578900</v>
       </c>
       <c r="I54" s="3">
-        <v>8621200</v>
+        <v>10184600</v>
       </c>
       <c r="J54" s="3">
-        <v>8252900</v>
+        <v>9801100</v>
       </c>
       <c r="K54" s="3">
         <v>7297900</v>
@@ -3147,25 +3147,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>867700</v>
+        <v>843500</v>
       </c>
       <c r="E57" s="3">
-        <v>927700</v>
+        <v>815100</v>
       </c>
       <c r="F57" s="3">
-        <v>866500</v>
+        <v>233900</v>
       </c>
       <c r="G57" s="3">
-        <v>882000</v>
+        <v>226700</v>
       </c>
       <c r="H57" s="3">
-        <v>811000</v>
+        <v>816400</v>
       </c>
       <c r="I57" s="3">
-        <v>854400</v>
+        <v>868000</v>
       </c>
       <c r="J57" s="3">
-        <v>836500</v>
+        <v>243900</v>
       </c>
       <c r="K57" s="3">
         <v>718700</v>
@@ -3203,25 +3203,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>275700</v>
+        <v>268000</v>
       </c>
       <c r="E58" s="3">
-        <v>883600</v>
+        <v>259000</v>
       </c>
       <c r="F58" s="3">
+        <v>857200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>831100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I58" s="3">
         <v>18900</v>
       </c>
-      <c r="G58" s="3">
-        <v>13100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>13200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>11900</v>
-      </c>
       <c r="J58" s="3">
-        <v>375000</v>
+        <v>13700</v>
       </c>
       <c r="K58" s="3">
         <v>53800</v>
@@ -3259,25 +3259,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>248300</v>
+        <v>232600</v>
       </c>
       <c r="E59" s="3">
-        <v>240200</v>
+        <v>224800</v>
       </c>
       <c r="F59" s="3">
-        <v>130200</v>
+        <v>252700</v>
       </c>
       <c r="G59" s="3">
-        <v>244200</v>
+        <v>245000</v>
       </c>
       <c r="H59" s="3">
-        <v>234900</v>
+        <v>78200</v>
       </c>
       <c r="I59" s="3">
-        <v>291200</v>
+        <v>83100</v>
       </c>
       <c r="J59" s="3">
-        <v>104200</v>
+        <v>310600</v>
       </c>
       <c r="K59" s="3">
         <v>179100</v>
@@ -3315,25 +3315,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1391800</v>
+        <v>1353000</v>
       </c>
       <c r="E60" s="3">
-        <v>2051500</v>
+        <v>1307400</v>
       </c>
       <c r="F60" s="3">
-        <v>1015500</v>
+        <v>1990400</v>
       </c>
       <c r="G60" s="3">
-        <v>1139300</v>
+        <v>1929700</v>
       </c>
       <c r="H60" s="3">
-        <v>1059100</v>
+        <v>956800</v>
       </c>
       <c r="I60" s="3">
-        <v>1157500</v>
+        <v>1017300</v>
       </c>
       <c r="J60" s="3">
-        <v>1315700</v>
+        <v>1189300</v>
       </c>
       <c r="K60" s="3">
         <v>951600</v>
@@ -3371,25 +3371,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1853200</v>
+        <v>1801500</v>
       </c>
       <c r="E61" s="3">
-        <v>1427300</v>
+        <v>1740800</v>
       </c>
       <c r="F61" s="3">
-        <v>1443500</v>
+        <v>1384800</v>
       </c>
       <c r="G61" s="3">
-        <v>1285600</v>
+        <v>1342600</v>
       </c>
       <c r="H61" s="3">
-        <v>1184000</v>
+        <v>1360000</v>
       </c>
       <c r="I61" s="3">
-        <v>1147700</v>
+        <v>1446000</v>
       </c>
       <c r="J61" s="3">
-        <v>609800</v>
+        <v>1341900</v>
       </c>
       <c r="K61" s="3">
         <v>964300</v>
@@ -3427,25 +3427,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1734700</v>
+        <v>1072700</v>
       </c>
       <c r="E62" s="3">
-        <v>1667800</v>
+        <v>1036500</v>
       </c>
       <c r="F62" s="3">
-        <v>2063600</v>
+        <v>1043900</v>
       </c>
       <c r="G62" s="3">
-        <v>1836700</v>
+        <v>1012000</v>
       </c>
       <c r="H62" s="3">
-        <v>1658000</v>
+        <v>1055500</v>
       </c>
       <c r="I62" s="3">
-        <v>1732200</v>
+        <v>1122200</v>
       </c>
       <c r="J62" s="3">
-        <v>1631300</v>
+        <v>990200</v>
       </c>
       <c r="K62" s="3">
         <v>1533500</v>
@@ -3651,25 +3651,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5156500</v>
+        <v>4840900</v>
       </c>
       <c r="E66" s="3">
-        <v>5308800</v>
+        <v>4677700</v>
       </c>
       <c r="F66" s="3">
-        <v>4701500</v>
+        <v>4993200</v>
       </c>
       <c r="G66" s="3">
-        <v>4425200</v>
+        <v>4841000</v>
       </c>
       <c r="H66" s="3">
-        <v>4063700</v>
+        <v>4261100</v>
       </c>
       <c r="I66" s="3">
-        <v>4147400</v>
+        <v>4530500</v>
       </c>
       <c r="J66" s="3">
-        <v>3631400</v>
+        <v>4448300</v>
       </c>
       <c r="K66" s="3">
         <v>3571200</v>
@@ -3953,25 +3953,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1226000</v>
+        <v>-766500</v>
       </c>
       <c r="E72" s="3">
-        <v>1526100</v>
+        <v>-740600</v>
       </c>
       <c r="F72" s="3">
-        <v>4245600</v>
+        <v>-463100</v>
       </c>
       <c r="G72" s="3">
-        <v>3744700</v>
+        <v>-448900</v>
       </c>
       <c r="H72" s="3">
-        <v>2356900</v>
+        <v>2029500</v>
       </c>
       <c r="I72" s="3">
-        <v>3254000</v>
+        <v>2157900</v>
       </c>
       <c r="J72" s="3">
-        <v>1678900</v>
+        <v>1987000</v>
       </c>
       <c r="K72" s="3">
         <v>2085900</v>
@@ -4177,25 +4177,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2445800</v>
+        <v>2377600</v>
       </c>
       <c r="E76" s="3">
-        <v>2745900</v>
+        <v>2297500</v>
       </c>
       <c r="F76" s="3">
-        <v>5465400</v>
+        <v>2664100</v>
       </c>
       <c r="G76" s="3">
-        <v>4964500</v>
+        <v>2582800</v>
       </c>
       <c r="H76" s="3">
-        <v>4872800</v>
+        <v>5149300</v>
       </c>
       <c r="I76" s="3">
-        <v>4473800</v>
+        <v>5474900</v>
       </c>
       <c r="J76" s="3">
-        <v>4621500</v>
+        <v>5182000</v>
       </c>
       <c r="K76" s="3">
         <v>3726700</v>
@@ -4297,22 +4297,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -4350,25 +4350,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-421000</v>
+        <v>-204700</v>
       </c>
       <c r="E81" s="3">
-        <v>-2546700</v>
+        <v>-197800</v>
       </c>
       <c r="F81" s="3">
-        <v>418300</v>
+        <v>-1235400</v>
       </c>
       <c r="G81" s="3">
-        <v>359500</v>
+        <v>-1197700</v>
       </c>
       <c r="H81" s="3">
-        <v>677100</v>
+        <v>197000</v>
       </c>
       <c r="I81" s="3">
-        <v>463100</v>
+        <v>209500</v>
       </c>
       <c r="J81" s="3">
-        <v>1399500</v>
+        <v>187600</v>
       </c>
       <c r="K81" s="3">
         <v>1084400</v>
@@ -4428,25 +4428,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>125600</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>133500</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>113500</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>107100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>98500</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>110200</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>140800</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4764,25 +4764,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>217300</v>
+        <v>108000</v>
       </c>
       <c r="E89" s="3">
-        <v>121300</v>
+        <v>104300</v>
       </c>
       <c r="F89" s="3">
-        <v>278500</v>
+        <v>107500</v>
       </c>
       <c r="G89" s="3">
-        <v>628500</v>
+        <v>104200</v>
       </c>
       <c r="H89" s="3">
-        <v>247300</v>
+        <v>225200</v>
       </c>
       <c r="I89" s="3">
-        <v>1068400</v>
+        <v>239400</v>
       </c>
       <c r="J89" s="3">
-        <v>749200</v>
+        <v>447900</v>
       </c>
       <c r="K89" s="3">
         <v>694500</v>
@@ -4842,25 +4842,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11147000</v>
+        <v>-305300</v>
       </c>
       <c r="E91" s="3">
-        <v>-11557000</v>
+        <v>-295000</v>
       </c>
       <c r="F91" s="3">
-        <v>-10854000</v>
+        <v>-315900</v>
       </c>
       <c r="G91" s="3">
-        <v>-9755000</v>
+        <v>-306300</v>
       </c>
       <c r="H91" s="3">
-        <v>-6144000</v>
+        <v>-288100</v>
       </c>
       <c r="I91" s="3">
-        <v>-7154000</v>
+        <v>-306300</v>
       </c>
       <c r="J91" s="3">
-        <v>-5586000</v>
+        <v>-286900</v>
       </c>
       <c r="K91" s="3">
         <v>-5481100</v>
@@ -5010,25 +5010,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-798700</v>
+        <v>-388200</v>
       </c>
       <c r="E94" s="3">
-        <v>-657000</v>
+        <v>-375100</v>
       </c>
       <c r="F94" s="3">
-        <v>-584900</v>
+        <v>-318700</v>
       </c>
       <c r="G94" s="3">
-        <v>-555000</v>
+        <v>-309000</v>
       </c>
       <c r="H94" s="3">
-        <v>-424000</v>
+        <v>-275500</v>
       </c>
       <c r="I94" s="3">
-        <v>-492800</v>
+        <v>-292900</v>
       </c>
       <c r="J94" s="3">
-        <v>-328100</v>
+        <v>-289700</v>
       </c>
       <c r="K94" s="3">
         <v>-276100</v>
@@ -5088,25 +5088,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>47100</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>93900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>99900</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>119800</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5312,25 +5312,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>23400</v>
+        <v>9000</v>
       </c>
       <c r="E100" s="3">
-        <v>732500</v>
+        <v>8700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1300</v>
+        <v>306700</v>
       </c>
       <c r="G100" s="3">
-        <v>-192900</v>
+        <v>297300</v>
       </c>
       <c r="H100" s="3">
-        <v>-4100</v>
+        <v>-94600</v>
       </c>
       <c r="I100" s="3">
-        <v>-382900</v>
+        <v>-100500</v>
       </c>
       <c r="J100" s="3">
-        <v>-87300</v>
+        <v>-220500</v>
       </c>
       <c r="K100" s="3">
         <v>44800</v>
@@ -5368,25 +5368,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5500</v>
+        <v>40900</v>
       </c>
       <c r="E101" s="3">
-        <v>-5100</v>
+        <v>43500</v>
       </c>
       <c r="F101" s="3">
-        <v>86900</v>
+        <v>27900</v>
       </c>
       <c r="G101" s="3">
-        <v>53400</v>
+        <v>26300</v>
       </c>
       <c r="H101" s="3">
-        <v>9200</v>
+        <v>5000</v>
       </c>
       <c r="I101" s="3">
-        <v>43700</v>
+        <v>5600</v>
       </c>
       <c r="J101" s="3">
-        <v>-3800</v>
+        <v>24300</v>
       </c>
       <c r="K101" s="3">
         <v>-17000</v>
@@ -5424,25 +5424,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-563500</v>
+        <v>-273900</v>
       </c>
       <c r="E102" s="3">
-        <v>191600</v>
+        <v>-264700</v>
       </c>
       <c r="F102" s="3">
-        <v>-220700</v>
+        <v>93000</v>
       </c>
       <c r="G102" s="3">
-        <v>-66000</v>
+        <v>90100</v>
       </c>
       <c r="H102" s="3">
-        <v>-171500</v>
+        <v>-104000</v>
       </c>
       <c r="I102" s="3">
-        <v>236400</v>
+        <v>-110600</v>
       </c>
       <c r="J102" s="3">
-        <v>330000</v>
+        <v>-34500</v>
       </c>
       <c r="K102" s="3">
         <v>446200</v>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -656,20 +656,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -677,244 +676,270 @@
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42735</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1507400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1649500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1512000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1461000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1451900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1407600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1607800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1709500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1997200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3938600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2937400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2617200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1267800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1661200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1587400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1755800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1279600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>945000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>840400</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1316400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1272000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1498800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1453100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1192900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1268300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1605700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2369400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2220700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2121800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1276900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1583900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1516400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1573800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1242100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>788400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>658500</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>227400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>248900</v>
+      </c>
+      <c r="F10" s="3">
         <v>195600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>189000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-46900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-45400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>414900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>441100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>391400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1569200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>716700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>495400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-9100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>77400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>71000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>182100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>37500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>156700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>181900</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +960,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,11 +1015,17 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1047,94 +1080,106 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-184800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-202200</v>
+      </c>
+      <c r="F14" s="3">
         <v>203500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>196600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>231900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>224800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-3800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>9400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>89500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>22000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>51000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-15000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>201200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>154400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>222800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-81400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>366400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400900</v>
+      </c>
+      <c r="F15" s="3">
         <v>113600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>109800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>922900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>894700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>125600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>133500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>-94800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1159,8 +1204,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1178,120 +1229,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1752100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1917300</v>
+      </c>
+      <c r="F17" s="3">
         <v>1495700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1445300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2546600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2468900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1375800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1462800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1580200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2470600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2258600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2183400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1270700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1795300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1548400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1735800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1472600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>727500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-244700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-267700</v>
+      </c>
+      <c r="F18" s="3">
         <v>16300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>15700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1094700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1061300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>232000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>246700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>416900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1467900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>678900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>433800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-134100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>39000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>20000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-193000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>217600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>118500</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1312,288 +1377,320 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-138500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-151500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-51600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-49800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>37300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>36200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-60400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-64200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>103300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-138400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-328300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-74600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>104800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>37000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-85200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-76400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-8900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>284700</v>
+      </c>
+      <c r="F21" s="3">
         <v>181400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>175300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-209100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-202700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>418000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>444400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>218800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1367900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>865400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>177800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>80100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>281500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-18700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-103100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>217300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F22" s="3">
         <v>48200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>46600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>32600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>31600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>33900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>36000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>30100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>39900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>52500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>51900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>47100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>70100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>65200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>77100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>78000</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>50700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-163300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-157800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1378700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1336600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>281100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>298900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>292200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1289600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>629000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>53600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-124600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-99400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>10800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-142300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-347400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>208700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F24" s="3">
         <v>32200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>31100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-142700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-138300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>74400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>79100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>96900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>152800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>109500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>21600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-115400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>62100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>5600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-166600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-27600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>39800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1648,120 +1745,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-195500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-188900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1236000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1198300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>206700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>219800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>195300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1136900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>519500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>32000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-161400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>24300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-319800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>168900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-204700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-197800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1235400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1197700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>197000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>209500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>187600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1084400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>501100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>16800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-13700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-160000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>24100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-319800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>179500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1816,8 +1931,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1872,8 +1993,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1928,8 +2055,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1984,120 +2117,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>151500</v>
+      </c>
+      <c r="F32" s="3">
         <v>51600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>49800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-37300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-36200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>60400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>64200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-103300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>138400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>328300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>74600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-104800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>85200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>76400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>8900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-204700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-197800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1235400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1197700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>197000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>209500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>187600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1084400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>501100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>16800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-13700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-160000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>24100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-319800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>179500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2152,125 +2303,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-204700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-197800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1235400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1197700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>197000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>209500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>187600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1084400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>501100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>16800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-13700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-160000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>24100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-319800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>179500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42735</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2291,8 +2460,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2313,64 +2484,72 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>930100</v>
+      </c>
+      <c r="F41" s="3">
         <v>852400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>823600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1397400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1354700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1176400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1250800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1533800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1101400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>642800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>297800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>321300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>158300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>139400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>135700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>434300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>55300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2425,128 +2604,146 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>390700</v>
+      </c>
+      <c r="F43" s="3">
         <v>553400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>534800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>474500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>460100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>466300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>495800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>463000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>383700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>258000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>267100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>295100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>456600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>434600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>422000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>389000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>346200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1353100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1480700</v>
+      </c>
+      <c r="F44" s="3">
         <v>1416900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1369200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1441300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1397300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1365000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1451300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1551900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1357900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>898200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>821500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>765500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>328900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>281200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>232000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>197200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>38700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4100</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
@@ -2572,253 +2769,283 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
-        <v>6500</v>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P45" s="3">
-        <v>84300</v>
+        <v>6500</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3" t="s">
+        <v>84300</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2563800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2805500</v>
+      </c>
+      <c r="F46" s="3">
         <v>2822700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2727600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3379800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3276700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3007700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3197900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3574100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2843000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1799000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1386400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1388400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>943800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>939500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>789700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1020500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>440200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>203200</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>573600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>627600</v>
+      </c>
+      <c r="F47" s="3">
         <v>585400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>565700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>564600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>547400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>670400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>712800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>694700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>350600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>326200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>250200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>242700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>251400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>197500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>166300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>174400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>143600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3551700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3886500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3388900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3274600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3384000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3280800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4960500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5274200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4540200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3313900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3535500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3065000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3057100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3388600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3532300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3384000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3620500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1556800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1326500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>119300</v>
+      </c>
+      <c r="F49" s="3">
         <v>108100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>104400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>27400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>26600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>485800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>516600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>489500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>389900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>446400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>363200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>371400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>427900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>465500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>420700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>453400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>53500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2873,8 +3100,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2929,64 +3162,76 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>416200</v>
+      </c>
+      <c r="F52" s="3">
         <v>377000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>364300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>352600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>341900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>337100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>358400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>359000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>400400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>311400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>290900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>273300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>262800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>248400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>243300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>227000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>190200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>159700</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3041,64 +3286,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7308200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7997200</v>
+      </c>
+      <c r="F54" s="3">
         <v>7390400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7141300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7814600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7576300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9578900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10184600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9801100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7297900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6418700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5355800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5332800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5274600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5383200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5004000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5495800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2384400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1876100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3119,8 +3376,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3141,344 +3400,382 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>826400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>904300</v>
+      </c>
+      <c r="F57" s="3">
         <v>843500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>815100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>233900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>226700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>816400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>868000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>243900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>718700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>631000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>607600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>598600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>488000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>453700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>440100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>476300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>296100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>221800</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>42100</v>
+      </c>
+      <c r="F58" s="3">
         <v>268000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>259000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>857200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>831100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>17800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>18900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>13700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>53800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>73400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>298800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>384300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>22200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>109000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>504100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>43000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>233100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>255100</v>
+      </c>
+      <c r="F59" s="3">
         <v>232600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>224800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>252700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>245000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>78200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>83100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>310600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>179100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>211600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>143700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>199200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>36500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>31900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>18500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1104500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1208600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1353000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1307400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1990400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1929700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>956800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1017300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1189300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>951600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>916000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>759200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1096600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>908800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>507900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>555000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>989700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>357600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>466900</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2189300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2395700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1801500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1740800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1384800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1342600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1360000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1446000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1341900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>964300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1352400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1270200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1181600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1137600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1882700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1578200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1507200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>469900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>835200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>913900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1072700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1036500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1043900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1012000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1055500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1122200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>990200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1533500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1693100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1676400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1424800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1692500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1298800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1292200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1396700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>615700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3533,8 +3830,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3589,8 +3892,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3645,64 +3954,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4750800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5198600</v>
+      </c>
+      <c r="F66" s="3">
         <v>4840900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4677700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4993200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4841000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4261100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4530500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4448300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3571200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4035800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3783500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3770300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3797100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3690800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3426700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3894700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1444200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1047600</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3723,8 +4044,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3779,8 +4102,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3835,8 +4164,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3891,8 +4226,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3947,64 +4288,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-731800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-800700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-766500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-740600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-463100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-448900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2029500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2157900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1987000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2085900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>212000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-582400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-628000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-675700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-609100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-703100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-709000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-301900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-413700</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4059,8 +4412,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4115,8 +4474,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4171,64 +4536,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2329200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2548800</v>
+      </c>
+      <c r="F76" s="3">
         <v>2377600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2297500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2664100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2582800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5149300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5474900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5182000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3726700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2382900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1572200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1562500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1477500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1692400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1577300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1601100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>940200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4283,125 +4660,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42735</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-204700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-197800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1235400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1197700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>197000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>209500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>187600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1084400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>501100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>16800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-13700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-160000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>24100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-319800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>179500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4422,38 +4817,40 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>139800</v>
+      </c>
+      <c r="F83" s="3">
         <v>125600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>133500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>113500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>107100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>98500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>110200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>140800</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -4478,8 +4875,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4534,8 +4937,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4590,8 +4999,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4646,8 +5061,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4702,8 +5123,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4758,64 +5185,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>183800</v>
+      </c>
+      <c r="F89" s="3">
         <v>108000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>104300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>107500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>104200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>225200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>239400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>447900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>694500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>768200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>431200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>71500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>612600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>154900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>108400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>72800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>110500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4836,64 +5275,72 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-276000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-302000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-305300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-295000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-315900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-306300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-288100</v>
       </c>
       <c r="I91" s="3">
         <v>-306300</v>
       </c>
       <c r="J91" s="3">
+        <v>-288100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-306300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-286900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5481100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4134500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-5122700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-139200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-249400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-203500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-237800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-165400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-136600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100700</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4948,8 +5395,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5004,64 +5457,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-269100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-294500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-388200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-375100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-318700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-309000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-275500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-292900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-289700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-276100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-259700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-269800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>12200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-292800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-201100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-243000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1627900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-223500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-316200</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5082,38 +5547,40 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F96" s="3">
         <v>2400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>2300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>48600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>47100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>93900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>99900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>119800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -5138,8 +5605,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5194,8 +5667,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5250,8 +5729,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5306,172 +5791,196 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>112100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>122700</v>
+      </c>
+      <c r="F100" s="3">
         <v>9000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>8700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>306700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>297300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-94600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-220500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>44800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-163800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-188000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>111900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-292100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>39900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-145300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1931800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>118600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>192600</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F101" s="3">
         <v>40900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>43500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>27900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>26300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>5600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>24300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>6400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-9700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>8800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-13500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-6900</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-273900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-264700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>93000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>90100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-104000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-110600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-34500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>446200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>342800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-20200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>185900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>27900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-293400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>369900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>5600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -820,10 +820,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1280000</v>
+        <v>1513300</v>
       </c>
       <c r="E9" s="3">
-        <v>1400700</v>
+        <v>1655900</v>
       </c>
       <c r="F9" s="3">
         <v>1316400</v>
@@ -882,10 +882,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>227400</v>
+        <v>-5900</v>
       </c>
       <c r="E10" s="3">
-        <v>248900</v>
+        <v>-6400</v>
       </c>
       <c r="F10" s="3">
         <v>195600</v>
@@ -1092,10 +1092,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-184800</v>
+        <v>-184700</v>
       </c>
       <c r="E14" s="3">
-        <v>-202200</v>
+        <v>-202100</v>
       </c>
       <c r="F14" s="3">
         <v>203500</v>
@@ -1104,10 +1104,10 @@
         <v>196600</v>
       </c>
       <c r="H14" s="3">
-        <v>231900</v>
+        <v>228700</v>
       </c>
       <c r="I14" s="3">
-        <v>224800</v>
+        <v>221800</v>
       </c>
       <c r="J14" s="3">
         <v>-3600</v>
@@ -1154,10 +1154,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>366400</v>
+        <v>133100</v>
       </c>
       <c r="E15" s="3">
-        <v>400900</v>
+        <v>145600</v>
       </c>
       <c r="F15" s="3">
         <v>113600</v>
@@ -1237,10 +1237,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1752100</v>
+        <v>1740100</v>
       </c>
       <c r="E17" s="3">
-        <v>1917300</v>
+        <v>1904100</v>
       </c>
       <c r="F17" s="3">
         <v>1495700</v>
@@ -1299,10 +1299,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-244700</v>
+        <v>-232700</v>
       </c>
       <c r="E18" s="3">
-        <v>-267700</v>
+        <v>-254600</v>
       </c>
       <c r="F18" s="3">
         <v>16300</v>
@@ -1385,10 +1385,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-126600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-138500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-151500</v>
       </c>
       <c r="F20" s="3">
         <v>-51600</v>
@@ -1397,10 +1397,10 @@
         <v>-49800</v>
       </c>
       <c r="H20" s="3">
-        <v>37300</v>
+        <v>40400</v>
       </c>
       <c r="I20" s="3">
-        <v>36200</v>
+        <v>39200</v>
       </c>
       <c r="J20" s="3">
         <v>-60400</v>
@@ -1447,10 +1447,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>260200</v>
+        <v>27000</v>
       </c>
       <c r="E21" s="3">
-        <v>284700</v>
+        <v>29600</v>
       </c>
       <c r="F21" s="3">
         <v>181400</v>
@@ -1459,10 +1459,10 @@
         <v>175300</v>
       </c>
       <c r="H21" s="3">
-        <v>-209100</v>
+        <v>-212200</v>
       </c>
       <c r="I21" s="3">
-        <v>-202700</v>
+        <v>-205800</v>
       </c>
       <c r="J21" s="3">
         <v>418000</v>
@@ -2129,10 +2129,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E32" s="3">
         <v>138500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>151500</v>
       </c>
       <c r="F32" s="3">
         <v>51600</v>
@@ -2141,10 +2141,10 @@
         <v>49800</v>
       </c>
       <c r="H32" s="3">
-        <v>-37300</v>
+        <v>-40400</v>
       </c>
       <c r="I32" s="3">
-        <v>-36200</v>
+        <v>-39200</v>
       </c>
       <c r="J32" s="3">
         <v>60400</v>
@@ -2616,10 +2616,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>357000</v>
+        <v>315000</v>
       </c>
       <c r="E43" s="3">
-        <v>390700</v>
+        <v>344700</v>
       </c>
       <c r="F43" s="3">
         <v>553400</v>
@@ -3408,10 +3408,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>826400</v>
+        <v>210900</v>
       </c>
       <c r="E57" s="3">
-        <v>904300</v>
+        <v>230800</v>
       </c>
       <c r="F57" s="3">
         <v>843500</v>
@@ -3532,10 +3532,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>233100</v>
+        <v>279000</v>
       </c>
       <c r="E59" s="3">
-        <v>255100</v>
+        <v>305300</v>
       </c>
       <c r="F59" s="3">
         <v>232600</v>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -656,23 +656,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -680,292 +679,318 @@
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2262200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2168400</v>
+      </c>
+      <c r="F8" s="3">
         <v>1542200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1490400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1507400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1649500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1512000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1461000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1451900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1407600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1607800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1709500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1997200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3938600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2937400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2617200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1267800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1661200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1587400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1755800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1279600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>945000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>840400</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1514900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1452100</v>
+      </c>
+      <c r="F9" s="3">
         <v>1077700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1041500</v>
       </c>
-      <c r="F9" s="3">
-        <v>1513300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1655900</v>
-      </c>
       <c r="H9" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="J9" s="3">
         <v>1316400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1272000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1498800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1453100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1192900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1268300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1605700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2369400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2220700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2121800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1276900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1583900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1516400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1573800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1242100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>788400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>658500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>747300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>716300</v>
+      </c>
+      <c r="F10" s="3">
         <v>464400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>448800</v>
       </c>
-      <c r="F10" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-6400</v>
-      </c>
       <c r="H10" s="3">
+        <v>227400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>248900</v>
+      </c>
+      <c r="J10" s="3">
         <v>195600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>189000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-46900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-45400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>414900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>441100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>391400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1569200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>716700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>495400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-9100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>77400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>71000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>182100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>37500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>156700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>181900</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -990,8 +1015,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,11 +1082,17 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1126,118 +1159,130 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>115700</v>
+      </c>
+      <c r="F14" s="3">
         <v>13400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>12900</v>
       </c>
-      <c r="F14" s="3">
-        <v>-184700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-202100</v>
-      </c>
       <c r="H14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J14" s="3">
         <v>-4500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-4400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>228700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>221800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-3800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>9400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>89500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>22000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>51000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-15000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>201200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>23000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>154400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>222800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-81400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>286600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>274700</v>
+      </c>
+      <c r="F15" s="3">
         <v>389100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>376100</v>
       </c>
-      <c r="F15" s="3">
-        <v>133100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>145600</v>
-      </c>
       <c r="H15" s="3">
+        <v>164800</v>
+      </c>
+      <c r="I15" s="3">
+        <v>180400</v>
+      </c>
+      <c r="J15" s="3">
         <v>322000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>311200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>922900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>894700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>125600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>133500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-94800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1262,8 +1307,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1285,144 +1336,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1956600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1875500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1544900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1493000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1740100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1904100</v>
-      </c>
       <c r="H17" s="3">
+        <v>1538500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1683600</v>
+      </c>
+      <c r="J17" s="3">
         <v>1704200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1646800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2546600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2468900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1375800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1462800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1580200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2470600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2258600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2183400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1270700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1795300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1548400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1735800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1472600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>727500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>305500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>292800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-232700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-254600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-192200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-185700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1094700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1061300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>232000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>246700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>416900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1467900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>678900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>433800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-134100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>39000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>20000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-193000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>217600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>118500</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1447,348 +1512,380 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>88400</v>
+      </c>
+      <c r="F20" s="3">
         <v>13900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>13400</v>
       </c>
-      <c r="F20" s="3">
-        <v>-126600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-138500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="J20" s="3">
         <v>-55800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-53900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>40400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>39200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-60400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-64200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>103300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-138400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-328300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-74600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>104800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>37000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-85200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-76400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-8900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>499900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>479100</v>
+      </c>
+      <c r="F21" s="3">
         <v>372600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>360100</v>
       </c>
-      <c r="F21" s="3">
-        <v>27000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>29600</v>
-      </c>
       <c r="H21" s="3">
+        <v>245800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>268900</v>
+      </c>
+      <c r="J21" s="3">
         <v>185600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>179400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-212200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-205800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>418000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>444400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>218800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1367900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>865400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>177800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>80100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>281500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-18700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-103100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>217300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>56100</v>
+      </c>
+      <c r="F22" s="3">
         <v>57500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>55600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>47900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>52400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>48200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>46600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>32600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>31600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>33900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>36000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>30100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>39900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>52500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>51900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>47100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>70100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>65200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>77100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>78000</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>58200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-68200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-65900</v>
       </c>
-      <c r="F23" s="3">
-        <v>46300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>50700</v>
-      </c>
       <c r="H23" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>46700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-159600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-154200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1378700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1336600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>281100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>298900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>292200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1289600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>629000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>53600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-124600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-99400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>10800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-142300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-347400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>208700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>82300</v>
+      </c>
+      <c r="F24" s="3">
         <v>41800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>40400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>8500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>9300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>32200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>31100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-142700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-138300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>74400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>79100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>96900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>152800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>109500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>21600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-115400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>62100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>5600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-166600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-27600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>39800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1855,144 +1952,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-110000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-106300</v>
       </c>
-      <c r="F26" s="3">
-        <v>37800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>41400</v>
-      </c>
       <c r="H26" s="3">
+        <v>34200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>37400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-191800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-185300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1236000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1198300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>206700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>219800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>195300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1136900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>519500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>32000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-161400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>24300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-319800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>168900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-101100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-97700</v>
       </c>
-      <c r="F27" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-1235400</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-1197700</v>
+      </c>
+      <c r="N27" s="3">
+        <v>197000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>209500</v>
+      </c>
+      <c r="P27" s="3">
+        <v>187600</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="R27" s="3">
+        <v>501100</v>
+      </c>
+      <c r="S27" s="3">
+        <v>16800</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="V27" s="3">
         <v>5100</v>
       </c>
-      <c r="H27" s="3">
-        <v>-200900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-194100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1235400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1197700</v>
-      </c>
-      <c r="L27" s="3">
-        <v>197000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>209500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>187600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1084400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>501100</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>16800</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>5100</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>24100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-319800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>179500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2059,8 +2174,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2127,8 +2248,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2195,8 +2322,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2263,144 +2396,162 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-92200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-88400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-13900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-13400</v>
       </c>
-      <c r="F32" s="3">
-        <v>126600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>138500</v>
-      </c>
       <c r="H32" s="3">
+        <v>112100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>122600</v>
+      </c>
+      <c r="J32" s="3">
         <v>55800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>53900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-40400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-39200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>60400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>64200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-103300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>138400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>328300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>74600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-104800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-37000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>85200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>76400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>8900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-101100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-97700</v>
       </c>
-      <c r="F33" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-1235400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-1197700</v>
+      </c>
+      <c r="N33" s="3">
+        <v>197000</v>
+      </c>
+      <c r="O33" s="3">
+        <v>209500</v>
+      </c>
+      <c r="P33" s="3">
+        <v>187600</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="R33" s="3">
+        <v>501100</v>
+      </c>
+      <c r="S33" s="3">
+        <v>16800</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="V33" s="3">
         <v>5100</v>
       </c>
-      <c r="H33" s="3">
-        <v>-200900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-194100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1235400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1197700</v>
-      </c>
-      <c r="L33" s="3">
-        <v>197000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>209500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>187600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1084400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>501100</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>16800</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="T33" s="3">
-        <v>5100</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>24100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-319800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>179500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2467,149 +2618,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-101100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-97700</v>
       </c>
-      <c r="F35" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-1235400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-1197700</v>
+      </c>
+      <c r="N35" s="3">
+        <v>197000</v>
+      </c>
+      <c r="O35" s="3">
+        <v>209500</v>
+      </c>
+      <c r="P35" s="3">
+        <v>187600</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="R35" s="3">
+        <v>501100</v>
+      </c>
+      <c r="S35" s="3">
+        <v>16800</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="V35" s="3">
         <v>5100</v>
       </c>
-      <c r="H35" s="3">
-        <v>-200900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-194100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1235400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1197700</v>
-      </c>
-      <c r="L35" s="3">
-        <v>197000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>209500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>187600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1084400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>501100</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>16800</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="T35" s="3">
-        <v>5100</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>24100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-319800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>179500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2634,8 +2803,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2660,76 +2831,84 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1037500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>994500</v>
+      </c>
+      <c r="F41" s="3">
         <v>1183300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1143600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>850000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>930100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>852400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>823600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1397400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1354700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1176400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1250800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1533800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1101400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>642800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>297800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>321300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>158300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>139400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>135700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>434300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>55300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2796,164 +2975,182 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>728700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>698500</v>
+      </c>
+      <c r="F43" s="3">
         <v>603800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>583500</v>
       </c>
-      <c r="F43" s="3">
-        <v>315000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>344700</v>
-      </c>
       <c r="H43" s="3">
+        <v>357000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>390700</v>
+      </c>
+      <c r="J43" s="3">
         <v>553400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>534800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>474500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>460100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>466300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>495800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>463000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>383700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>258000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>267100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>295100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>456600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>434600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>422000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>389000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>346200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1901300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1822500</v>
+      </c>
+      <c r="F44" s="3">
         <v>1595700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1542100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1353100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1480700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1416900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1369200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1441300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1397300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1365000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1451300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1551900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1357900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>898200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>821500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>765500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>328900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>281200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>232000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>197200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>38700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
         <v>17200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>16600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -2979,301 +3176,331 @@
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R45" s="3">
-        <v>6500</v>
+      <c r="R45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T45" s="3">
-        <v>84300</v>
+        <v>6500</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="s">
+        <v>84300</v>
+      </c>
+      <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3669300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3517100</v>
+      </c>
+      <c r="F46" s="3">
         <v>3400100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3285900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2563800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2805500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2822700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2727600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3379800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3276700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3007700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3197900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3574100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2843000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1799000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1386400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1388400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>943800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>939500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>789700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1020500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>440200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>203200</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>654200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>627000</v>
+      </c>
+      <c r="F47" s="3">
         <v>541500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>523400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>573600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>627600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>585400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>565700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>564600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>547400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>670400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>712800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>694700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>350600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>326200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>250200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>242700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>251400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>197500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>166300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>174400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>143600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3916800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3754400</v>
+      </c>
+      <c r="F48" s="3">
         <v>3531000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3412400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3551700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3886500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3388900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3274600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3384000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3280800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4960500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5274200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4540200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3313900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3535500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3065000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3057100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3388600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3532300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3384000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3620500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1556800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1326500</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>114200</v>
+      </c>
+      <c r="F49" s="3">
         <v>112300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>108500</v>
       </c>
-      <c r="F49" s="3">
-        <v>109000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>119300</v>
-      </c>
       <c r="H49" s="3">
+        <v>114100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>124800</v>
+      </c>
+      <c r="J49" s="3">
         <v>108100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>104400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>27400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>26600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>485800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>516600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>489500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>389900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>446400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>363200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>371400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>427900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>465500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>420700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>453400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>53500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3340,8 +3567,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3408,76 +3641,88 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>557800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>534600</v>
+      </c>
+      <c r="F52" s="3">
         <v>438800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>424000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>380400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>416200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>377000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>364300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>352600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>341900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>337100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>358400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>359000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>400400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>311400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>290900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>273300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>262800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>248400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>243300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>227000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>190200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>159700</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3544,76 +3789,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9043600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8668600</v>
+      </c>
+      <c r="F54" s="3">
         <v>8149000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7875300</v>
       </c>
-      <c r="F54" s="3">
-        <v>7308200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>7997200</v>
-      </c>
       <c r="H54" s="3">
+        <v>7313300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>8002700</v>
+      </c>
+      <c r="J54" s="3">
         <v>7390400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7141300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7814600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7576300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9578900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10184600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9801100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7297900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6418700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5355800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5332800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5274600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5383200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5004000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5495800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2384400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1876100</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3638,8 +3895,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3664,416 +3923,454 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>970000</v>
+      </c>
+      <c r="F57" s="3">
         <v>876100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>846700</v>
       </c>
-      <c r="F57" s="3">
-        <v>210900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>230800</v>
-      </c>
       <c r="H57" s="3">
+        <v>826400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>904300</v>
+      </c>
+      <c r="J57" s="3">
         <v>843500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>815100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>233900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>226700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>816400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>868000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>243900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>718700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>631000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>607600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>598600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>488000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>453700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>440100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>476300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>296100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>221800</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>698700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>669700</v>
+      </c>
+      <c r="F58" s="3">
         <v>25900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>25000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>38500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>42100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>268000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>259000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>857200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>831100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>17800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>18900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>13700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>53800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>73400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>7900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>298800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>384300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>22200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>109000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>504100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>43000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>285400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>273600</v>
+      </c>
+      <c r="F59" s="3">
         <v>247400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>239100</v>
       </c>
-      <c r="F59" s="3">
-        <v>279000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>305300</v>
-      </c>
       <c r="H59" s="3">
+        <v>238200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>260600</v>
+      </c>
+      <c r="J59" s="3">
         <v>232600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>224800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>252700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>245000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>78200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>83100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>310600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>179100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>211600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>143700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>199200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>36500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>31900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>9300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>18500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2063000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1977500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1176900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1137400</v>
       </c>
-      <c r="F60" s="3">
-        <v>1104500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1208600</v>
-      </c>
       <c r="H60" s="3">
+        <v>1109600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>1214200</v>
+      </c>
+      <c r="J60" s="3">
         <v>1353000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1307400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1990400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1929700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>956800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1017300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1189300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>951600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>916000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>759200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1096600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>908800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>507900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>555000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>989700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>357600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>466900</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1953000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1872000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2387700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2307500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2189300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2395700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1801500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1740800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1384800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1342600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1360000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1446000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1341900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>964300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1352400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1270200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1181600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1137600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1882700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1578200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1507200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>469900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1114200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="F62" s="3">
         <v>912100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>881500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>835200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>913900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1072700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1036500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1043900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1012000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1055500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1122200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>990200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1533500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1693100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1676400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1424800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1692500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1298800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1292200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1396700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>615700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>403300</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4140,8 +4437,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4208,8 +4511,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4276,76 +4585,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6376100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6111700</v>
+      </c>
+      <c r="F66" s="3">
         <v>5651600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5461800</v>
       </c>
-      <c r="F66" s="3">
-        <v>4750800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>5198600</v>
-      </c>
       <c r="H66" s="3">
+        <v>4755800</v>
+      </c>
+      <c r="I66" s="3">
+        <v>5204200</v>
+      </c>
+      <c r="J66" s="3">
         <v>4840900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4677700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4993200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4841000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4261100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4530500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4448300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3571200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4035800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3783500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3770300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3797100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3690800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3426700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3894700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1444200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1047600</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4370,8 +4691,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4438,8 +4761,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4506,8 +4835,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4574,8 +4909,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4642,76 +4983,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1152500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1104700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-980400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-947400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-731800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-800700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-766500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-740600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-463100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-448900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2029500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2157900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1987000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2085900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>212000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-582400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-628000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-675700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-609100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-703100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-709000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-301900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-413700</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4778,8 +5131,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4846,8 +5205,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4914,76 +5279,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2387200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2288300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2273600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2197300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2329200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2548800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2377600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2297500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2664100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2582800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5149300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5474900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5182000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3726700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2382900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1572200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1562500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1477500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1692400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1577300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1601100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>940200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5050,149 +5427,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-101100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-97700</v>
       </c>
-      <c r="F81" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-1235400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-1197700</v>
+      </c>
+      <c r="N81" s="3">
+        <v>197000</v>
+      </c>
+      <c r="O81" s="3">
+        <v>209500</v>
+      </c>
+      <c r="P81" s="3">
+        <v>187600</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="R81" s="3">
+        <v>501100</v>
+      </c>
+      <c r="S81" s="3">
+        <v>16800</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="V81" s="3">
         <v>5100</v>
       </c>
-      <c r="H81" s="3">
-        <v>-200900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-194100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1235400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1197700</v>
-      </c>
-      <c r="L81" s="3">
-        <v>197000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>209500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>187600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1084400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>501100</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>16800</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="T81" s="3">
-        <v>5100</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>24100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-319800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>179500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5217,50 +5612,52 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>135500</v>
+      </c>
+      <c r="F83" s="3">
         <v>113200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>109400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>144200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>139800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>125600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>133500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>113500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>107100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>98500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>110200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>140800</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5285,8 +5682,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5353,8 +5756,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5421,8 +5830,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5489,8 +5904,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5557,8 +5978,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5625,76 +6052,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>257700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>247000</v>
+      </c>
+      <c r="F89" s="3">
         <v>371000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>358600</v>
       </c>
-      <c r="F89" s="3">
-        <v>168000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>183800</v>
-      </c>
       <c r="H89" s="3">
+        <v>174500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>190900</v>
+      </c>
+      <c r="J89" s="3">
         <v>101300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>97800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>107500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>104200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>225200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>239400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>447900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>694500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>768200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>431200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>71500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>612600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>154900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>108400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>72800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>110500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5719,76 +6158,84 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-325200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-311700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-268600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-259600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-276000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-302000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-305300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-295000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-315900</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-306300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-288100</v>
       </c>
       <c r="M91" s="3">
         <v>-306300</v>
       </c>
       <c r="N91" s="3">
+        <v>-288100</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-306300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-286900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-5481100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4134500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5122700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-139200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-249400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-203500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-237800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-165400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-136600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-100700</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5855,8 +6302,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5923,76 +6376,88 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-378600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-362900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-257800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-249200</v>
       </c>
-      <c r="F94" s="3">
-        <v>-269100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-294500</v>
-      </c>
       <c r="H94" s="3">
+        <v>-273400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-299100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-383900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-370900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-318700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-309000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-275500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-292900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-289700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-276100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-259700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-269800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>12200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-292800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-201100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-243000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1627900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-223500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-316200</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6017,50 +6482,52 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>48600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>47100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>93900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>99900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>119800</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6085,8 +6552,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6153,8 +6626,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6221,8 +6700,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6289,208 +6774,232 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F100" s="3">
         <v>40900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>39500</v>
       </c>
-      <c r="F100" s="3">
-        <v>112100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>122700</v>
-      </c>
       <c r="H100" s="3">
+        <v>109800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>120200</v>
+      </c>
+      <c r="J100" s="3">
         <v>11400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>306700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>297300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-94600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-220500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>44800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-163800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-188000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>111900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-292100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>39900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-145300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1931800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>118600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>192600</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>40900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>43500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>27900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>26300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>5600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>24300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-17000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>6400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-9700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>8800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-13500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-6900</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="F102" s="3">
         <v>139800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>135100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>12900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>14200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-273900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-264700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>93000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>90100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-104000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-110600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-34500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>446200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>342800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-20200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>185900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>27900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-293400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>369900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>5600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBSW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>SBSW</t>
   </si>
@@ -847,10 +847,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1514900</v>
+        <v>1797800</v>
       </c>
       <c r="E9" s="3">
-        <v>1452100</v>
+        <v>1723200</v>
       </c>
       <c r="F9" s="3">
         <v>1077700</v>
@@ -859,10 +859,10 @@
         <v>1041500</v>
       </c>
       <c r="H9" s="3">
-        <v>1280000</v>
+        <v>1513300</v>
       </c>
       <c r="I9" s="3">
-        <v>1400700</v>
+        <v>1655900</v>
       </c>
       <c r="J9" s="3">
         <v>1316400</v>
@@ -921,10 +921,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>747300</v>
+        <v>464400</v>
       </c>
       <c r="E10" s="3">
-        <v>716300</v>
+        <v>445100</v>
       </c>
       <c r="F10" s="3">
         <v>464400</v>
@@ -933,10 +933,10 @@
         <v>448800</v>
       </c>
       <c r="H10" s="3">
-        <v>227400</v>
+        <v>-5900</v>
       </c>
       <c r="I10" s="3">
-        <v>248900</v>
+        <v>-6400</v>
       </c>
       <c r="J10" s="3">
         <v>195600</v>
@@ -1171,10 +1171,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>120700</v>
+        <v>121500</v>
       </c>
       <c r="E14" s="3">
-        <v>115700</v>
+        <v>116400</v>
       </c>
       <c r="F14" s="3">
         <v>13400</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>286600</v>
+        <v>2900</v>
       </c>
       <c r="E15" s="3">
-        <v>274700</v>
+        <v>2800</v>
       </c>
       <c r="F15" s="3">
         <v>389100</v>
@@ -1257,10 +1257,10 @@
         <v>376100</v>
       </c>
       <c r="H15" s="3">
-        <v>164800</v>
+        <v>-68500</v>
       </c>
       <c r="I15" s="3">
-        <v>180400</v>
+        <v>-74900</v>
       </c>
       <c r="J15" s="3">
         <v>322000</v>
@@ -1344,10 +1344,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1956600</v>
+        <v>1955900</v>
       </c>
       <c r="E17" s="3">
-        <v>1875500</v>
+        <v>1874800</v>
       </c>
       <c r="F17" s="3">
         <v>1544900</v>
@@ -1418,10 +1418,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>305500</v>
+        <v>306300</v>
       </c>
       <c r="E18" s="3">
-        <v>292800</v>
+        <v>293600</v>
       </c>
       <c r="F18" s="3">
         <v>-2700</v>
@@ -1594,10 +1594,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>499900</v>
+        <v>217000</v>
       </c>
       <c r="E21" s="3">
-        <v>479100</v>
+        <v>208000</v>
       </c>
       <c r="F21" s="3">
         <v>372600</v>
@@ -1606,10 +1606,10 @@
         <v>360100</v>
       </c>
       <c r="H21" s="3">
-        <v>245800</v>
+        <v>12500</v>
       </c>
       <c r="I21" s="3">
-        <v>268900</v>
+        <v>13600</v>
       </c>
       <c r="J21" s="3">
         <v>185600</v>
@@ -2987,10 +2987,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>728700</v>
+        <v>688800</v>
       </c>
       <c r="E43" s="3">
-        <v>698500</v>
+        <v>660300</v>
       </c>
       <c r="F43" s="3">
         <v>603800</v>
@@ -2999,10 +2999,10 @@
         <v>583500</v>
       </c>
       <c r="H43" s="3">
-        <v>357000</v>
+        <v>315000</v>
       </c>
       <c r="I43" s="3">
-        <v>390700</v>
+        <v>344700</v>
       </c>
       <c r="J43" s="3">
         <v>553400</v>
@@ -3931,10 +3931,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1012000</v>
+        <v>205700</v>
       </c>
       <c r="E57" s="3">
-        <v>970000</v>
+        <v>197200</v>
       </c>
       <c r="F57" s="3">
         <v>876100</v>
@@ -3943,10 +3943,10 @@
         <v>846700</v>
       </c>
       <c r="H57" s="3">
-        <v>826400</v>
+        <v>210900</v>
       </c>
       <c r="I57" s="3">
-        <v>904300</v>
+        <v>230800</v>
       </c>
       <c r="J57" s="3">
         <v>843500</v>
@@ -4079,10 +4079,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>285400</v>
+        <v>357800</v>
       </c>
       <c r="E59" s="3">
-        <v>273600</v>
+        <v>343000</v>
       </c>
       <c r="F59" s="3">
         <v>247400</v>
@@ -4091,10 +4091,10 @@
         <v>239100</v>
       </c>
       <c r="H59" s="3">
-        <v>238200</v>
+        <v>284100</v>
       </c>
       <c r="I59" s="3">
-        <v>260600</v>
+        <v>310900</v>
       </c>
       <c r="J59" s="3">
         <v>232600</v>
@@ -5620,10 +5620,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>123800</v>
+        <v>120500</v>
       </c>
       <c r="E83" s="3">
-        <v>135500</v>
+        <v>131800</v>
       </c>
       <c r="F83" s="3">
         <v>113200</v>
@@ -6064,25 +6064,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>257700</v>
+        <v>253800</v>
       </c>
       <c r="E89" s="3">
-        <v>247000</v>
+        <v>243200</v>
       </c>
       <c r="F89" s="3">
-        <v>371000</v>
+        <v>374700</v>
       </c>
       <c r="G89" s="3">
-        <v>358600</v>
+        <v>362100</v>
       </c>
       <c r="H89" s="3">
-        <v>174500</v>
+        <v>172200</v>
       </c>
       <c r="I89" s="3">
-        <v>190900</v>
+        <v>188400</v>
       </c>
       <c r="J89" s="3">
-        <v>101300</v>
+        <v>103600</v>
       </c>
       <c r="K89" s="3">
         <v>97800</v>
@@ -6490,25 +6490,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>9100</v>
+        <v>5200</v>
       </c>
       <c r="E96" s="3">
-        <v>8700</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
+        <v>5000</v>
+      </c>
+      <c r="F96" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G96" s="3">
+        <v>3500</v>
       </c>
       <c r="H96" s="3">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="I96" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
+        <v>2500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>2400</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
@@ -6786,25 +6786,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>30200</v>
+        <v>34100</v>
       </c>
       <c r="E100" s="3">
-        <v>29000</v>
+        <v>32700</v>
       </c>
       <c r="F100" s="3">
-        <v>40900</v>
+        <v>37300</v>
       </c>
       <c r="G100" s="3">
-        <v>39500</v>
+        <v>36000</v>
       </c>
       <c r="H100" s="3">
-        <v>109800</v>
+        <v>112100</v>
       </c>
       <c r="I100" s="3">
-        <v>120200</v>
+        <v>122700</v>
       </c>
       <c r="J100" s="3">
-        <v>11400</v>
+        <v>9000</v>
       </c>
       <c r="K100" s="3">
         <v>11000</v>
